--- a/Book_H1_tags.xlsx
+++ b/Book_H1_tags.xlsx
@@ -5150,48 +5150,56 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="4" t="inlineStr">
+      <c r="A177" t="inlineStr">
         <is>
           <t>Cma Dish Machines</t>
         </is>
       </c>
-      <c r="B177" s="4" t="inlineStr">
+      <c r="B177" t="inlineStr">
         <is>
           <t>13417.92</t>
         </is>
       </c>
-      <c r="C177" s="4" t="inlineStr"/>
-      <c r="D177" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E177" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Cma Dish Machines Dishwasher Heater Control Thermostat (12kW) - 13417.92</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>GWX-200, EST models</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="4" t="inlineStr">
+      <c r="A178" t="inlineStr">
         <is>
           <t>Cma Dish Machines</t>
         </is>
       </c>
-      <c r="B178" s="4" t="inlineStr">
+      <c r="B178" t="inlineStr">
         <is>
           <t>13417.94</t>
         </is>
       </c>
-      <c r="C178" s="4" t="inlineStr"/>
-      <c r="D178" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E178" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Cma Dish Machines Dishwasher Thermostat Assembly - 13417.94</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Parts Town: fits five CMA models</t>
         </is>
       </c>
     </row>

--- a/Book_H1_tags.xlsx
+++ b/Book_H1_tags.xlsx
@@ -5547,4602 +5547,5354 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="4" t="inlineStr">
+      <c r="A192" s="2" t="inlineStr">
         <is>
           <t>Duke</t>
         </is>
       </c>
-      <c r="B192" s="4" t="inlineStr">
+      <c r="B192" s="2" t="inlineStr">
         <is>
           <t>115114</t>
         </is>
       </c>
-      <c r="C192" s="4" t="inlineStr"/>
-      <c r="D192" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E192" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C192" s="2" t="inlineStr">
+        <is>
+          <t>Duke Dishwasher Rubber Pump Hose, Left Hand (K1000/5000) - 115114</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E192" s="2" t="inlineStr">
+        <is>
+          <t>Parts Town and eBay; dishwasher category inferred from Parts Town page</t>
         </is>
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="4" t="inlineStr">
+      <c r="A193" t="inlineStr">
         <is>
           <t>Duke</t>
         </is>
       </c>
-      <c r="B193" s="4" t="inlineStr">
+      <c r="B193" t="inlineStr">
         <is>
           <t>155828</t>
         </is>
       </c>
-      <c r="C193" s="4" t="inlineStr"/>
-      <c r="D193" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E193" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Duke Convection Oven Motor Assembly 1/2 HP 2-Speed 220V - 155828</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Parts Town and many sellers; two outlier listings ignored</t>
         </is>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="4" t="inlineStr">
+      <c r="A194" s="2" t="inlineStr">
         <is>
           <t>Duke</t>
         </is>
       </c>
-      <c r="B194" s="4" t="inlineStr">
+      <c r="B194" s="2" t="inlineStr">
         <is>
           <t>212100</t>
         </is>
       </c>
-      <c r="C194" s="4" t="inlineStr"/>
-      <c r="D194" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E194" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C194" s="2" t="inlineStr">
+        <is>
+          <t>Duke Food Warmer Toggle Switch 3-Pole 3-Phase 220V - 212100</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E194" s="2" t="inlineStr">
+        <is>
+          <t>Fits EP-6/E-4/ASI3E per one seller; one listing says hot/cold food wells</t>
         </is>
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="4" t="inlineStr">
+      <c r="A195" s="2" t="inlineStr">
         <is>
           <t>Duke</t>
         </is>
       </c>
-      <c r="B195" s="4" t="inlineStr">
+      <c r="B195" s="2" t="inlineStr">
         <is>
           <t>214317</t>
         </is>
       </c>
-      <c r="C195" s="4" t="inlineStr"/>
-      <c r="D195" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E195" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C195" s="2" t="inlineStr">
+        <is>
+          <t>Duke Soup Station Gasket Kit - 214317</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E195" s="2" t="inlineStr">
+        <is>
+          <t>Single source: Duke HCSS soup station holding unit manual</t>
         </is>
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="4" t="inlineStr">
+      <c r="A196" s="3" t="inlineStr">
         <is>
           <t>Duke</t>
         </is>
       </c>
-      <c r="B196" s="4" t="inlineStr">
+      <c r="B196" s="3" t="inlineStr">
         <is>
           <t>217098</t>
         </is>
       </c>
-      <c r="C196" s="4" t="inlineStr"/>
-      <c r="D196" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E196" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>Duke Air Filter 10" x 24" x 1" (RUF-48) - 217098</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="inlineStr">
+        <is>
+          <t>Parts Town only; equipment type not stated</t>
         </is>
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="4" t="inlineStr">
+      <c r="A197" t="inlineStr">
         <is>
           <t>Duke</t>
         </is>
       </c>
-      <c r="B197" s="4" t="inlineStr">
+      <c r="B197" t="inlineStr">
         <is>
           <t>218829</t>
         </is>
       </c>
-      <c r="C197" s="4" t="inlineStr"/>
-      <c r="D197" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E197" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Duke Soup Station Transformer 208/240V to 24V 30VA - 218829</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Duke HCSS-LH manual and Parts Town</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="4" t="inlineStr">
+      <c r="A198" s="3" t="inlineStr">
         <is>
           <t>Duke</t>
         </is>
       </c>
-      <c r="B198" s="4" t="inlineStr">
+      <c r="B198" s="3" t="inlineStr">
         <is>
           <t>230363</t>
         </is>
       </c>
-      <c r="C198" s="4" t="inlineStr"/>
-      <c r="D198" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E198" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C198" s="3" t="inlineStr">
+        <is>
+          <t>Duke Drain Support Plate - 230363</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E198" s="3" t="inlineStr">
+        <is>
+          <t>Sellers agree on part; no equipment type named</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="4" t="inlineStr">
+      <c r="A199" s="2" t="inlineStr">
         <is>
           <t>Duke</t>
         </is>
       </c>
-      <c r="B199" s="4" t="inlineStr">
+      <c r="B199" s="2" t="inlineStr">
         <is>
           <t>2503911</t>
         </is>
       </c>
-      <c r="C199" s="4" t="inlineStr"/>
-      <c r="D199" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E199" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C199" s="2" t="inlineStr">
+        <is>
+          <t>Duke Sandwich Unit Replacement Cord Kit (SSL Clearview Day) - 2503911</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E199" s="2" t="inlineStr">
+        <is>
+          <t>Duke Subway clear-view day cover parts list; type inferred</t>
         </is>
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="4" t="inlineStr">
+      <c r="A200" t="inlineStr">
         <is>
           <t>Duke</t>
         </is>
       </c>
-      <c r="B200" s="4" t="inlineStr">
+      <c r="B200" t="inlineStr">
         <is>
           <t>512299</t>
         </is>
       </c>
-      <c r="C200" s="4" t="inlineStr"/>
-      <c r="D200" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E200" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Duke Proofer Proofer Lights &amp; Beeper Harness - 512299</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>TSC-3/9, TSC-6/18 proofer cabinets</t>
         </is>
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="4" t="inlineStr">
+      <c r="A201" t="inlineStr">
         <is>
           <t>Duke</t>
         </is>
       </c>
-      <c r="B201" s="4" t="inlineStr">
+      <c r="B201" t="inlineStr">
         <is>
           <t>512905</t>
         </is>
       </c>
-      <c r="C201" s="4" t="inlineStr"/>
-      <c r="D201" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E201" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Duke Proofer Oven Door Handle &amp; Strike Plate - 512905</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>AHPO-6/18 Gold, TSC models</t>
         </is>
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="4" t="inlineStr">
+      <c r="A202" t="inlineStr">
         <is>
           <t>Edlund</t>
         </is>
       </c>
-      <c r="B202" s="4" t="inlineStr">
+      <c r="B202" t="inlineStr">
         <is>
           <t>P055</t>
         </is>
       </c>
-      <c r="C202" s="4" t="inlineStr"/>
-      <c r="D202" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E202" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Edlund Scale Platform with Studs (EDL-10) - P055</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Many sellers agree</t>
         </is>
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="4" t="inlineStr">
+      <c r="A203" s="3" t="inlineStr">
         <is>
           <t>Electrolux</t>
         </is>
       </c>
-      <c r="B203" s="4" t="inlineStr">
+      <c r="B203" s="3" t="inlineStr">
         <is>
           <t>48706</t>
         </is>
       </c>
-      <c r="C203" s="4" t="inlineStr"/>
-      <c r="D203" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E203" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C203" s="3" t="inlineStr"/>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
+      <c r="E203" s="3" t="inlineStr">
+        <is>
+          <t>Searched "48706" Electrolux; only a ZIP code and a GE bulb number found</t>
         </is>
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="4" t="inlineStr">
+      <c r="A204" s="3" t="inlineStr">
         <is>
           <t>Electrolux</t>
         </is>
       </c>
-      <c r="B204" s="4" t="inlineStr">
+      <c r="B204" s="3" t="inlineStr">
         <is>
           <t>56921</t>
         </is>
       </c>
-      <c r="C204" s="4" t="inlineStr"/>
-      <c r="D204" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E204" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C204" s="3" t="inlineStr"/>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
+      <c r="E204" s="3" t="inlineStr">
+        <is>
+          <t>Searched "56921" Electrolux; matches belong to other brands (Amica, Keating)</t>
         </is>
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="4" t="inlineStr">
+      <c r="A205" s="2" t="inlineStr">
         <is>
           <t>Electrolux Pro</t>
         </is>
       </c>
-      <c r="B205" s="4" t="inlineStr">
+      <c r="B205" s="2" t="inlineStr">
         <is>
           <t>6879</t>
         </is>
       </c>
-      <c r="C205" s="4" t="inlineStr"/>
-      <c r="D205" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E205" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>Electrolux Pro Contactor 3-Pole with Auxiliary Contact - 6879</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E205" s="2" t="inlineStr">
+        <is>
+          <t>Listed as 006879; fits ECF/E6-T per Parts Town; type not confirmed</t>
         </is>
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="4" t="inlineStr">
+      <c r="A206" s="2" t="inlineStr">
         <is>
           <t>Electrolux Pro</t>
         </is>
       </c>
-      <c r="B206" s="4" t="inlineStr">
+      <c r="B206" s="2" t="inlineStr">
         <is>
           <t>0C9974</t>
         </is>
       </c>
-      <c r="C206" s="4" t="inlineStr"/>
-      <c r="D206" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E206" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>Electrolux Pro Grill Ribbed Plate Scraper - 0C9974</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E206" s="2" t="inlineStr">
+        <is>
+          <t>Electrolux Professional store and catalog; fits grill models</t>
         </is>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="4" t="inlineStr">
+      <c r="A207" s="2" t="inlineStr">
         <is>
           <t>Electrolux Pro</t>
         </is>
       </c>
-      <c r="B207" s="4" t="inlineStr">
+      <c r="B207" s="2" t="inlineStr">
         <is>
           <t>0CA504</t>
         </is>
       </c>
-      <c r="C207" s="4" t="inlineStr"/>
-      <c r="D207" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E207" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>Electrolux Pro Griddle Smooth Plate Heating Element 800W 208V - 0CA504</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E207" s="2" t="inlineStr">
+        <is>
+          <t>Speedelight parts manual; no retailer listing</t>
         </is>
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="4" t="inlineStr">
+      <c r="A208" t="inlineStr">
         <is>
           <t>Electrolux Pro</t>
         </is>
       </c>
-      <c r="B208" s="4" t="inlineStr">
+      <c r="B208" t="inlineStr">
         <is>
           <t>0CK270</t>
         </is>
       </c>
-      <c r="C208" s="4" t="inlineStr"/>
-      <c r="D208" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E208" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Electrolux Pro Combi Oven Boiler Temperature Probe 1200mm - 0CK270</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Skyline combi ovens; several sellers and catalog</t>
         </is>
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="4" t="inlineStr">
+      <c r="A209" s="2" t="inlineStr">
         <is>
           <t>Electrolux Pro</t>
         </is>
       </c>
-      <c r="B209" s="4" t="inlineStr">
+      <c r="B209" s="2" t="inlineStr">
         <is>
           <t>0D7602</t>
         </is>
       </c>
-      <c r="C209" s="4" t="inlineStr"/>
-      <c r="D209" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E209" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C209" s="2" t="inlineStr">
+        <is>
+          <t>Electrolux Pro Vegetable Spinner Power Cord 220V - 0D7602</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E209" s="2" t="inlineStr">
+        <is>
+          <t>SP-VP2 parts manual lists it; eBay sellers</t>
         </is>
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="4" t="inlineStr">
+      <c r="A210" s="2" t="inlineStr">
         <is>
           <t>Electrolux Pro</t>
         </is>
       </c>
-      <c r="B210" s="4" t="inlineStr">
+      <c r="B210" s="2" t="inlineStr">
         <is>
           <t>0D7962</t>
         </is>
       </c>
-      <c r="C210" s="4" t="inlineStr"/>
-      <c r="D210" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E210" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C210" s="2" t="inlineStr">
+        <is>
+          <t>Electrolux Pro Mixer Power Board, 1 Speed, 3 Phase - 0D7962</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E210" s="2" t="inlineStr">
+        <is>
+          <t>Parts Town and Maran-Pro (Dito mixer parts); replaces 0KJ778</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="4" t="inlineStr">
+      <c r="A211" t="inlineStr">
         <is>
           <t>Fbd</t>
         </is>
       </c>
-      <c r="B211" s="4" t="inlineStr">
+      <c r="B211" t="inlineStr">
         <is>
           <t>12-2546-S001</t>
         </is>
       </c>
-      <c r="C211" s="4" t="inlineStr"/>
-      <c r="D211" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E211" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Fbd Frozen Beverage Dispenser Plastic Drip Tray Drain Kit - 12-2546-S001</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>AllPoints and Parts Town; replaces 12-2546-0001</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="4" t="inlineStr">
+      <c r="A212" t="inlineStr">
         <is>
           <t>Fbd</t>
         </is>
       </c>
-      <c r="B212" s="4" t="inlineStr">
+      <c r="B212" t="inlineStr">
         <is>
           <t>12-2602-0002</t>
         </is>
       </c>
-      <c r="C212" s="4" t="inlineStr"/>
-      <c r="D212" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E212" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Fbd Frozen Beverage Dispenser Thermistor Kit IP68 58" - 12-2602-0002</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Parts Town, eBay and Apex agree</t>
         </is>
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="4" t="inlineStr">
+      <c r="A213" s="2" t="inlineStr">
         <is>
           <t>Fbd</t>
         </is>
       </c>
-      <c r="B213" s="4" t="inlineStr">
+      <c r="B213" s="2" t="inlineStr">
         <is>
           <t>12-2787-0108</t>
         </is>
       </c>
-      <c r="C213" s="4" t="inlineStr"/>
-      <c r="D213" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E213" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C213" s="2" t="inlineStr">
+        <is>
+          <t>Fbd Frozen Beverage Dispenser Active Charge Regulator with Fitting - 12-2787-0108</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E213" s="2" t="inlineStr">
+        <is>
+          <t>Single seller (Webstaurant) lists it as slushy/granita regulator</t>
         </is>
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="4" t="inlineStr">
+      <c r="A214" t="inlineStr">
         <is>
           <t>Fbd</t>
         </is>
       </c>
-      <c r="B214" s="4" t="inlineStr">
+      <c r="B214" t="inlineStr">
         <is>
           <t>12-2867-0306</t>
         </is>
       </c>
-      <c r="C214" s="4" t="inlineStr"/>
-      <c r="D214" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E214" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Fbd Frozen Beverage Dispenser CO2 Gas Module .017 Orifice with 100 PSI Gauge - 12-2867-0306</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>FBD56X parts catalog and distributors</t>
         </is>
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="4" t="inlineStr">
+      <c r="A215" s="2" t="inlineStr">
         <is>
           <t>Federal Industries</t>
         </is>
       </c>
-      <c r="B215" s="4" t="inlineStr">
+      <c r="B215" s="2" t="inlineStr">
         <is>
           <t>30-18054</t>
         </is>
       </c>
-      <c r="C215" s="4" t="inlineStr"/>
-      <c r="D215" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E215" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>Federal Industries Display Case Compressor 1 HP R404A 208-230V - 30-18054</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>Sellers differ on HP/voltage; refrigerated case type inferred</t>
         </is>
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="4" t="inlineStr">
+      <c r="A216" s="2" t="inlineStr">
         <is>
           <t>Federal Industries</t>
         </is>
       </c>
-      <c r="B216" s="4" t="inlineStr">
+      <c r="B216" s="2" t="inlineStr">
         <is>
           <t>30-18057</t>
         </is>
       </c>
-      <c r="C216" s="4" t="inlineStr"/>
-      <c r="D216" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E216" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>Federal Industries Display Case Compressor 1/3 HP R134a 115V - 30-18057</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>Sellers agree on part; case type inferred</t>
         </is>
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="4" t="inlineStr">
+      <c r="A217" s="2" t="inlineStr">
         <is>
           <t>Federal Industries</t>
         </is>
       </c>
-      <c r="B217" s="4" t="inlineStr">
+      <c r="B217" s="2" t="inlineStr">
         <is>
           <t>32-19865-2</t>
         </is>
       </c>
-      <c r="C217" s="4" t="inlineStr"/>
-      <c r="D217" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E217" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>Federal Industries Display Case Carel Control Module 230V - 32-19865-2</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>Control module; case type inferred</t>
         </is>
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="4" t="inlineStr">
+      <c r="A218" s="2" t="inlineStr">
         <is>
           <t>Federal Industries</t>
         </is>
       </c>
-      <c r="B218" s="4" t="inlineStr">
+      <c r="B218" s="2" t="inlineStr">
         <is>
           <t>32-21342-18</t>
         </is>
       </c>
-      <c r="C218" s="4" t="inlineStr"/>
-      <c r="D218" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E218" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>Federal Industries Display Case Electronic Temperature Controller Kit 240V (VRSS RF) - 32-21342-18</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>Case type inferred; -17 variant also exists</t>
         </is>
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="4" t="inlineStr">
+      <c r="A219" s="3" t="inlineStr">
         <is>
           <t>Federal Industries</t>
         </is>
       </c>
-      <c r="B219" s="4" t="inlineStr">
+      <c r="B219" s="3" t="inlineStr">
         <is>
           <t>33-20658-A</t>
         </is>
       </c>
-      <c r="C219" s="4" t="inlineStr"/>
-      <c r="D219" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E219" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C219" s="3" t="inlineStr"/>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
+      <c r="E219" s="3" t="inlineStr">
+        <is>
+          <t>Searched "33-20658-A" Federal Industries; no matching listing found</t>
         </is>
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="4" t="inlineStr">
+      <c r="A220" t="inlineStr">
         <is>
           <t>Federal Industries</t>
         </is>
       </c>
-      <c r="B220" s="4" t="inlineStr">
+      <c r="B220" t="inlineStr">
         <is>
           <t>41-11066</t>
         </is>
       </c>
-      <c r="C220" s="4" t="inlineStr"/>
-      <c r="D220" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E220" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Federal Industries Display Case Rocker Switch On/Off 22A - 41-11066</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Federal service document and sellers</t>
         </is>
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="4" t="inlineStr">
+      <c r="A221" s="2" t="inlineStr">
         <is>
           <t>Federal Industries</t>
         </is>
       </c>
-      <c r="B221" s="4" t="inlineStr">
+      <c r="B221" s="2" t="inlineStr">
         <is>
           <t>41-14324</t>
         </is>
       </c>
-      <c r="C221" s="4" t="inlineStr"/>
-      <c r="D221" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E221" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C221" s="2" t="inlineStr">
+        <is>
+          <t>Federal Industries Display Case Remote Solenoid Valve Coil - 41-14324</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="inlineStr">
+        <is>
+          <t>RSSM/RSSL series; sellers differ on voltage</t>
         </is>
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="4" t="inlineStr">
+      <c r="A222" s="2" t="inlineStr">
         <is>
           <t>Federal Industries</t>
         </is>
       </c>
-      <c r="B222" s="4" t="inlineStr">
+      <c r="B222" s="2" t="inlineStr">
         <is>
           <t>43-12269</t>
         </is>
       </c>
-      <c r="C222" s="4" t="inlineStr"/>
-      <c r="D222" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E222" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C222" s="2" t="inlineStr">
+        <is>
+          <t>Federal Industries Display Case Wire Harness with 5-Pin Connector - 43-12269</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="inlineStr">
+        <is>
+          <t>Sellers disagree on length; -1 variant is 72"; fits SN48-3SC</t>
         </is>
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="4" t="inlineStr">
+      <c r="A223" s="2" t="inlineStr">
         <is>
           <t>Federal Industries</t>
         </is>
       </c>
-      <c r="B223" s="4" t="inlineStr">
+      <c r="B223" s="2" t="inlineStr">
         <is>
           <t>479-904</t>
         </is>
       </c>
-      <c r="C223" s="4" t="inlineStr"/>
-      <c r="D223" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E223" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>Federal Industries Display Case Energy Saving Night Curtain - 479-904</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>Parts Town and RSSM/RSSD manual (refrigerated self-service merchandiser)</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="4" t="inlineStr">
+      <c r="A224" t="inlineStr">
         <is>
           <t>Federal Industries</t>
         </is>
       </c>
-      <c r="B224" s="4" t="inlineStr">
+      <c r="B224" t="inlineStr">
         <is>
           <t>78-10270</t>
         </is>
       </c>
-      <c r="C224" s="4" t="inlineStr"/>
-      <c r="D224" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E224" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Federal Industries Display Case Rubber Shelf Cushion #129 (FCCR-4/5/6) - 78-10270</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Parts Town and several sellers</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="4" t="inlineStr">
+      <c r="A225" s="2" t="inlineStr">
         <is>
           <t>Federal Industries</t>
         </is>
       </c>
-      <c r="B225" s="4" t="inlineStr">
+      <c r="B225" s="2" t="inlineStr">
         <is>
           <t>M12705-3</t>
         </is>
       </c>
-      <c r="C225" s="4" t="inlineStr"/>
-      <c r="D225" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E225" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>Federal Industries Display Case Display Pan (7550 Case) - M12705-3</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>Single seller listing; function inferred from title</t>
         </is>
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="4" t="inlineStr">
+      <c r="A226" s="2" t="inlineStr">
         <is>
           <t>Follett</t>
         </is>
       </c>
-      <c r="B226" s="4" t="inlineStr">
+      <c r="B226" s="2" t="inlineStr">
         <is>
           <t>938647</t>
         </is>
       </c>
-      <c r="C226" s="4" t="inlineStr"/>
-      <c r="D226" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E226" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>Follett Ice Machine OCS Water Sensor Wiring Assembly - 938647</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>Two seller listings</t>
         </is>
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="4" t="inlineStr">
+      <c r="A227" s="2" t="inlineStr">
         <is>
           <t>Follett</t>
         </is>
       </c>
-      <c r="B227" s="4" t="inlineStr">
+      <c r="B227" s="2" t="inlineStr">
         <is>
           <t>957811</t>
         </is>
       </c>
-      <c r="C227" s="4" t="inlineStr"/>
-      <c r="D227" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E227" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>Follett Ice Machine Gearmotor Assembly (7 Series) - 957811</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>Listed as 00957811; no model fit list</t>
         </is>
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="4" t="inlineStr">
+      <c r="A228" t="inlineStr">
         <is>
           <t>Follett</t>
         </is>
       </c>
-      <c r="B228" s="4" t="inlineStr">
+      <c r="B228" t="inlineStr">
         <is>
           <t>957829</t>
         </is>
       </c>
-      <c r="C228" s="4" t="inlineStr"/>
-      <c r="D228" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E228" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Follett Ice Machine Main Housing Assembly (7 Series) - 957829</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Many sellers; fits 7FS/7UD/7UC</t>
         </is>
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="4" t="inlineStr">
+      <c r="A229" s="2" t="inlineStr">
         <is>
           <t>Follett</t>
         </is>
       </c>
-      <c r="B229" s="4" t="inlineStr">
+      <c r="B229" s="2" t="inlineStr">
         <is>
           <t>957837</t>
         </is>
       </c>
-      <c r="C229" s="4" t="inlineStr"/>
-      <c r="D229" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E229" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>Follett Ice Machine Main Housing Screw (7 Series) - 957837</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>AllPoints, Sharptek, eBay</t>
         </is>
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="4" t="inlineStr">
+      <c r="A230" t="inlineStr">
         <is>
           <t>Follett</t>
         </is>
       </c>
-      <c r="B230" s="4" t="inlineStr">
+      <c r="B230" t="inlineStr">
         <is>
           <t>957944</t>
         </is>
       </c>
-      <c r="C230" s="4" t="inlineStr"/>
-      <c r="D230" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E230" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Follett Ice Machine Water Option Kit (7 Series) - 957944</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Many sellers agree</t>
         </is>
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="4" t="inlineStr">
+      <c r="A231" s="3" t="inlineStr">
         <is>
           <t>Follett</t>
         </is>
       </c>
-      <c r="B231" s="4" t="inlineStr">
+      <c r="B231" s="3" t="inlineStr">
         <is>
           <t>968917</t>
         </is>
       </c>
-      <c r="C231" s="4" t="inlineStr"/>
-      <c r="D231" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E231" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C231" s="3" t="inlineStr"/>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
+      <c r="E231" s="3" t="inlineStr">
+        <is>
+          <t>Searched "968917" Follett; no matching part listing found</t>
         </is>
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="4" t="inlineStr">
+      <c r="A232" s="2" t="inlineStr">
         <is>
           <t>Follett</t>
         </is>
       </c>
-      <c r="B232" s="4" t="inlineStr">
+      <c r="B232" s="2" t="inlineStr">
         <is>
           <t>996579</t>
         </is>
       </c>
-      <c r="C232" s="4" t="inlineStr"/>
-      <c r="D232" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E232" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>Follett Refrigerator Hinge Assembly, Right Hand - 996579</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>Listed as 00996579; fits Follett REF-45 / REF20-25 units</t>
         </is>
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="4" t="inlineStr">
+      <c r="A233" s="2" t="inlineStr">
         <is>
           <t>Follett</t>
         </is>
       </c>
-      <c r="B233" s="4" t="inlineStr">
+      <c r="B233" s="2" t="inlineStr">
         <is>
           <t>1054154</t>
         </is>
       </c>
-      <c r="C233" s="4" t="inlineStr"/>
-      <c r="D233" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E233" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>Follett Ice Machine Evaporator Drain Tube (12# LA-41) - 1054154</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>Single source: Follett 2023 parts price list, shown as 01054154</t>
         </is>
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="4" t="inlineStr">
+      <c r="A234" s="2" t="inlineStr">
         <is>
           <t>Follett</t>
         </is>
       </c>
-      <c r="B234" s="4" t="inlineStr">
+      <c r="B234" s="2" t="inlineStr">
         <is>
           <t>1159482</t>
         </is>
       </c>
-      <c r="C234" s="4" t="inlineStr"/>
-      <c r="D234" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E234" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>Follett Ice Machine Water Dispense Solenoid Valve 120V 3/8" - 1159482</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>Two seller listings; no model fit list</t>
         </is>
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="4" t="inlineStr">
+      <c r="A235" s="2" t="inlineStr">
         <is>
           <t>Follett</t>
         </is>
       </c>
-      <c r="B235" s="4" t="inlineStr">
+      <c r="B235" s="2" t="inlineStr">
         <is>
           <t>1441526</t>
         </is>
       </c>
-      <c r="C235" s="4" t="inlineStr"/>
-      <c r="D235" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E235" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>Follett Ice Machine Rear Fill Solenoid Valve 120V (Elite) - 1441526</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>Listed as 01441526; several sellers</t>
         </is>
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="4" t="inlineStr">
+      <c r="A236" s="2" t="inlineStr">
         <is>
           <t>Follett</t>
         </is>
       </c>
-      <c r="B236" s="4" t="inlineStr">
+      <c r="B236" s="2" t="inlineStr">
         <is>
           <t>PB500343</t>
         </is>
       </c>
-      <c r="C236" s="4" t="inlineStr"/>
-      <c r="D236" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E236" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>Follett Ice Machine Hinge Pin, All Lift Doors (Set of 2) - PB500343</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>Many sellers agree on part; no model fit list</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="4" t="inlineStr">
+      <c r="A237" t="inlineStr">
         <is>
           <t>Follett</t>
         </is>
       </c>
-      <c r="B237" s="4" t="inlineStr">
+      <c r="B237" t="inlineStr">
         <is>
           <t>PB502200</t>
         </is>
       </c>
-      <c r="C237" s="4" t="inlineStr"/>
-      <c r="D237" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E237" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Follett Ice Machine Rear Cart Wheel 8" - PB502200</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Fits DEV ice cart models</t>
         </is>
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="4" t="inlineStr">
+      <c r="A238" t="inlineStr">
         <is>
           <t>Follett</t>
         </is>
       </c>
-      <c r="B238" s="4" t="inlineStr">
+      <c r="B238" t="inlineStr">
         <is>
           <t>PD501333</t>
         </is>
       </c>
-      <c r="C238" s="4" t="inlineStr"/>
-      <c r="D238" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E238" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Follett Ice Dispenser Wheel Motor Shaft Seal - PD501333</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>U150 / CVU155N dispensers</t>
         </is>
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="4" t="inlineStr">
+      <c r="A239" s="2" t="inlineStr">
         <is>
           <t>Follett</t>
         </is>
       </c>
-      <c r="B239" s="4" t="inlineStr">
+      <c r="B239" s="2" t="inlineStr">
         <is>
           <t>PD502357</t>
         </is>
       </c>
-      <c r="C239" s="4" t="inlineStr"/>
-      <c r="D239" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E239" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>Follett Ice Machine Water Valve Solenoid Assembly 120V 60Hz - PD502357</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>Many sellers agree; no model fit list</t>
         </is>
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="4" t="inlineStr">
+      <c r="A240" t="inlineStr">
         <is>
           <t>Follett</t>
         </is>
       </c>
-      <c r="B240" s="4" t="inlineStr">
+      <c r="B240" t="inlineStr">
         <is>
           <t>PD502414</t>
         </is>
       </c>
-      <c r="C240" s="4" t="inlineStr"/>
-      <c r="D240" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E240" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Follett Ice Machine Ice Baffle with Securing Hardware - PD502414</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Fits 12CI400A / C12HI400A models</t>
         </is>
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="4" t="inlineStr">
+      <c r="A241" t="inlineStr">
         <is>
           <t>Follett</t>
         </is>
       </c>
-      <c r="B241" s="4" t="inlineStr">
+      <c r="B241" t="inlineStr">
         <is>
           <t>PD502685</t>
         </is>
       </c>
-      <c r="C241" s="4" t="inlineStr"/>
-      <c r="D241" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E241" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Follett Ice Machine Drain Tube Assembly (25/50 Series) - PD502685</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>25CR/50CR400A models</t>
         </is>
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="4" t="inlineStr">
+      <c r="A242" t="inlineStr">
         <is>
           <t>Follett</t>
         </is>
       </c>
-      <c r="B242" s="4" t="inlineStr">
+      <c r="B242" t="inlineStr">
         <is>
           <t>PD502915</t>
         </is>
       </c>
-      <c r="C242" s="4" t="inlineStr"/>
-      <c r="D242" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E242" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Follett Ice Machine SensorSAFE Control Board 230V (E25/50) - PD502915</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Fits C/E25 and C/E50 ice machines</t>
         </is>
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="4" t="inlineStr">
+      <c r="A243" t="inlineStr">
         <is>
           <t>Follett</t>
         </is>
       </c>
-      <c r="B243" s="4" t="inlineStr">
+      <c r="B243" t="inlineStr">
         <is>
           <t>PI500672</t>
         </is>
       </c>
-      <c r="C243" s="4" t="inlineStr"/>
-      <c r="D243" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E243" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Follett Ice Dispenser Condensate Fan Motor 115V 9W - PI500672</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>12 Series dispensers and R5A/W icemaker</t>
         </is>
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="4" t="inlineStr">
+      <c r="A244" t="inlineStr">
         <is>
           <t>Follett</t>
         </is>
       </c>
-      <c r="B244" s="4" t="inlineStr">
+      <c r="B244" t="inlineStr">
         <is>
           <t>PI501111</t>
         </is>
       </c>
-      <c r="C244" s="4" t="inlineStr"/>
-      <c r="D244" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E244" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Follett Ice Machine Multi-Purpose Grease 14 oz (Chevron SRI-2) - PI501111</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>Follett ice makers and dispensers</t>
         </is>
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="4" t="inlineStr">
+      <c r="A245" t="inlineStr">
         <is>
           <t>Follett</t>
         </is>
       </c>
-      <c r="B245" s="4" t="inlineStr">
+      <c r="B245" t="inlineStr">
         <is>
           <t>PI501588</t>
         </is>
       </c>
-      <c r="C245" s="4" t="inlineStr"/>
-      <c r="D245" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E245" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Follett Ice Machine Compressor Start Relay - PI501588</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>12CI/12HI400A series</t>
         </is>
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="4" t="inlineStr">
+      <c r="A246" s="2" t="inlineStr">
         <is>
           <t>Electrolux</t>
         </is>
       </c>
-      <c r="B246" s="4" t="inlineStr">
+      <c r="B246" s="2" t="inlineStr">
         <is>
           <t>0CBAN3</t>
         </is>
       </c>
-      <c r="C246" s="4" t="inlineStr"/>
-      <c r="D246" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E246" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>Electrolux Gas Oven Spark Electrode Kit with Gaskets - 0CBAN3</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>Electrolux Professional Skyline/Magistar gas ovens; brand given as Electrolux</t>
         </is>
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="4" t="inlineStr">
+      <c r="A247" t="inlineStr">
         <is>
           <t>Frymaster</t>
         </is>
       </c>
-      <c r="B247" s="4" t="inlineStr">
+      <c r="B247" t="inlineStr">
         <is>
           <t>1062568SP</t>
         </is>
       </c>
-      <c r="C247" s="4" t="inlineStr"/>
-      <c r="D247" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E247" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Frymaster Fryer Wash Down Hose Assembly - 1062568SP</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Fits HD260, HD1814G, SR38G</t>
         </is>
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="4" t="inlineStr">
+      <c r="A248" t="inlineStr">
         <is>
           <t>Frymaster</t>
         </is>
       </c>
-      <c r="B248" s="4" t="inlineStr">
+      <c r="B248" t="inlineStr">
         <is>
           <t>1086713</t>
         </is>
       </c>
-      <c r="C248" s="4" t="inlineStr"/>
-      <c r="D248" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E248" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Frymaster Fryer Float Switch (GWC Noodles) - 1086713</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Many sellers agree</t>
         </is>
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="4" t="inlineStr">
+      <c r="A249" t="inlineStr">
         <is>
           <t>Frymaster</t>
         </is>
       </c>
-      <c r="B249" s="4" t="inlineStr">
+      <c r="B249" t="inlineStr">
         <is>
           <t>8030099</t>
         </is>
       </c>
-      <c r="C249" s="4" t="inlineStr"/>
-      <c r="D249" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E249" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Frymaster Fryer Full-Size Basket - 8030099</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Many sellers agree</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="4" t="inlineStr">
+      <c r="A250" t="inlineStr">
         <is>
           <t>Frymaster</t>
         </is>
       </c>
-      <c r="B250" s="4" t="inlineStr">
+      <c r="B250" t="inlineStr">
         <is>
           <t>8064206</t>
         </is>
       </c>
-      <c r="C250" s="4" t="inlineStr"/>
-      <c r="D250" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E250" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Frymaster Fryer Temperature Probe Assembly (Minco) - 8064206</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Many sellers and service bulletin</t>
         </is>
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="4" t="inlineStr">
+      <c r="A251" t="inlineStr">
         <is>
           <t>Frymaster</t>
         </is>
       </c>
-      <c r="B251" s="4" t="inlineStr">
+      <c r="B251" t="inlineStr">
         <is>
           <t>8068530SP</t>
         </is>
       </c>
-      <c r="C251" s="4" t="inlineStr"/>
-      <c r="D251" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E251" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Frymaster Fryer Resistor Assembly 120V (Basket Lift) - 8068530SP</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Parts Town and many sellers</t>
         </is>
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="4" t="inlineStr">
+      <c r="A252" t="inlineStr">
         <is>
           <t>Frymaster</t>
         </is>
       </c>
-      <c r="B252" s="4" t="inlineStr">
+      <c r="B252" t="inlineStr">
         <is>
           <t>8102744</t>
         </is>
       </c>
-      <c r="C252" s="4" t="inlineStr"/>
-      <c r="D252" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E252" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Frymaster Fryer Leaf Filter 13.25" x 13.25" (MF90 Series) - 8102744</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Parts Town and many sellers</t>
         </is>
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="4" t="inlineStr">
+      <c r="A253" t="inlineStr">
         <is>
           <t>Frymaster</t>
         </is>
       </c>
-      <c r="B253" s="4" t="inlineStr">
+      <c r="B253" t="inlineStr">
         <is>
           <t>8122025</t>
         </is>
       </c>
-      <c r="C253" s="4" t="inlineStr"/>
-      <c r="D253" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E253" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Frymaster Fryer Sanagrid Filter Screen - 8122025</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Frymaster FilterQuick parts manual and sellers</t>
         </is>
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="4" t="inlineStr">
+      <c r="A254" t="inlineStr">
         <is>
           <t>Frymaster</t>
         </is>
       </c>
-      <c r="B254" s="4" t="inlineStr">
+      <c r="B254" t="inlineStr">
         <is>
           <t>826-2013</t>
         </is>
       </c>
-      <c r="C254" s="4" t="inlineStr"/>
-      <c r="D254" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E254" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Frymaster Fryer Thermostat 200-400°F, 36" Capillary - 826-2013</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Frymaster components manual and many sellers</t>
         </is>
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="4" t="inlineStr">
+      <c r="A255" t="inlineStr">
         <is>
           <t>Frymaster</t>
         </is>
       </c>
-      <c r="B255" s="4" t="inlineStr">
+      <c r="B255" t="inlineStr">
         <is>
           <t>8261177</t>
         </is>
       </c>
-      <c r="C255" s="4" t="inlineStr"/>
-      <c r="D255" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E255" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Frymaster Fryer Hi-Limit Safety Thermostat Kit 425°F - 8261177</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>MH52/BIH52 series; many sellers</t>
         </is>
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="4" t="inlineStr">
+      <c r="A256" s="2" t="inlineStr">
         <is>
           <t>Frymaster</t>
         </is>
       </c>
-      <c r="B256" s="4" t="inlineStr">
+      <c r="B256" s="2" t="inlineStr">
         <is>
           <t>8261549</t>
         </is>
       </c>
-      <c r="C256" s="4" t="inlineStr"/>
-      <c r="D256" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E256" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>Frymaster Heated Landing Zone Heater &amp; Tape Kit 208V (HLZ) - 8261549</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>Parts Town and Amazon; one reseller lists as Manitowoc</t>
         </is>
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="4" t="inlineStr">
+      <c r="A257" t="inlineStr">
         <is>
           <t>Frymaster</t>
         </is>
       </c>
-      <c r="B257" s="4" t="inlineStr">
+      <c r="B257" t="inlineStr">
         <is>
           <t>8261551</t>
         </is>
       </c>
-      <c r="C257" s="4" t="inlineStr"/>
-      <c r="D257" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E257" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Frymaster Heated Landing Zone Blower Motor Kit with Tape 208/240V (HLZ/HPT) - 8261551</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Parts Town and many sellers</t>
         </is>
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="4" t="inlineStr">
+      <c r="A258" t="inlineStr">
         <is>
           <t>Frymaster</t>
         </is>
       </c>
-      <c r="B258" s="4" t="inlineStr">
+      <c r="B258" t="inlineStr">
         <is>
           <t>8261756</t>
         </is>
       </c>
-      <c r="C258" s="4" t="inlineStr"/>
-      <c r="D258" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E258" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Frymaster Fryer Pump Motor and Gasket Kit 1/3 HP 208V - 8261756</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Fits 3FQG30U, BIRE14, FPRE217/222</t>
         </is>
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="4" t="inlineStr">
+      <c r="A259" t="inlineStr">
         <is>
           <t>Frymaster</t>
         </is>
       </c>
-      <c r="B259" s="4" t="inlineStr">
+      <c r="B259" t="inlineStr">
         <is>
           <t>8261817</t>
         </is>
       </c>
-      <c r="C259" s="4" t="inlineStr"/>
-      <c r="D259" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E259" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Frymaster Fryer Natural Gas to LP Conversion Kit (Honeywell, SR42) - 8261817</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Parts Town and many sellers</t>
         </is>
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="4" t="inlineStr">
+      <c r="A260" t="inlineStr">
         <is>
           <t>Frymaster</t>
         </is>
       </c>
-      <c r="B260" s="4" t="inlineStr">
+      <c r="B260" t="inlineStr">
         <is>
           <t>8262286</t>
         </is>
       </c>
-      <c r="C260" s="4" t="inlineStr"/>
-      <c r="D260" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E260" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Frymaster Fryer CM3.5 Digital Controller, Gas FV H50 - 8262286</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Many sellers agree</t>
         </is>
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="4" t="inlineStr">
+      <c r="A261" t="inlineStr">
         <is>
           <t>Frymaster</t>
         </is>
       </c>
-      <c r="B261" s="4" t="inlineStr">
+      <c r="B261" t="inlineStr">
         <is>
           <t>8262287</t>
         </is>
       </c>
-      <c r="C261" s="4" t="inlineStr"/>
-      <c r="D261" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E261" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Frymaster Fryer CM3.5 Digital Controller, Gas Dual Vat H50 - 8262287</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Frymaster components manual and sellers</t>
         </is>
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="4" t="inlineStr">
+      <c r="A262" t="inlineStr">
         <is>
           <t>Frymaster</t>
         </is>
       </c>
-      <c r="B262" s="4" t="inlineStr">
+      <c r="B262" t="inlineStr">
         <is>
           <t>8262332</t>
         </is>
       </c>
-      <c r="C262" s="4" t="inlineStr"/>
-      <c r="D262" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E262" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Frymaster Fryer Electric Full Vat Controller (SMT) - 8262332</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Parts Town and many sellers</t>
         </is>
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="4" t="inlineStr">
+      <c r="A263" t="inlineStr">
         <is>
           <t>Frymaster</t>
         </is>
       </c>
-      <c r="B263" s="4" t="inlineStr">
+      <c r="B263" t="inlineStr">
         <is>
           <t>8262385</t>
         </is>
       </c>
-      <c r="C263" s="4" t="inlineStr"/>
-      <c r="D263" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E263" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Frymaster Fryer Basket Lift Timer Assembly, Gas Full Vat (H50/SMT) - 8262385</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Parts Town and many sellers</t>
         </is>
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="4" t="inlineStr">
+      <c r="A264" t="inlineStr">
         <is>
           <t>Frymaster</t>
         </is>
       </c>
-      <c r="B264" s="4" t="inlineStr">
+      <c r="B264" t="inlineStr">
         <is>
           <t>8262455</t>
         </is>
       </c>
-      <c r="C264" s="4" t="inlineStr"/>
-      <c r="D264" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E264" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Frymaster Fryer Hi-Limit Kit 415°F - 8262455</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Frymaster BIELA14 parts manual and sellers</t>
         </is>
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="4" t="inlineStr">
+      <c r="A265" t="inlineStr">
         <is>
           <t>Frymaster</t>
         </is>
       </c>
-      <c r="B265" s="4" t="inlineStr">
+      <c r="B265" t="inlineStr">
         <is>
           <t>8262456</t>
         </is>
       </c>
-      <c r="C265" s="4" t="inlineStr"/>
-      <c r="D265" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E265" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Frymaster Fryer Hi-Limit Thermostat Kit 435°F - 8262456</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Parts Town and many sellers</t>
         </is>
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="4" t="inlineStr">
+      <c r="A266" t="inlineStr">
         <is>
           <t>Frymaster</t>
         </is>
       </c>
-      <c r="B266" s="4" t="inlineStr">
+      <c r="B266" t="inlineStr">
         <is>
           <t>8262505</t>
         </is>
       </c>
-      <c r="C266" s="4" t="inlineStr"/>
-      <c r="D266" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E266" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Frymaster Fryer Full Vat H55 8-Second Controller with Harness - 8262505</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Many sellers; descriptions vary slightly</t>
         </is>
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="4" t="inlineStr">
+      <c r="A267" t="inlineStr">
         <is>
           <t>Frymaster</t>
         </is>
       </c>
-      <c r="B267" s="4" t="inlineStr">
+      <c r="B267" t="inlineStr">
         <is>
           <t>8263196</t>
         </is>
       </c>
-      <c r="C267" s="4" t="inlineStr"/>
-      <c r="D267" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E267" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Frymaster Fryer Gas OCF/LOV Temperature Probe Kit - 8263196</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Many sellers agree</t>
         </is>
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="4" t="inlineStr">
+      <c r="A268" s="3" t="inlineStr">
         <is>
           <t>Gaylord</t>
         </is>
       </c>
-      <c r="B268" s="4" t="inlineStr">
+      <c r="B268" s="3" t="inlineStr">
         <is>
           <t>10222</t>
         </is>
       </c>
-      <c r="C268" s="4" t="inlineStr"/>
-      <c r="D268" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E268" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C268" s="3" t="inlineStr">
+        <is>
+          <t>Gaylord Detergent Pump 120V - 10222</t>
+        </is>
+      </c>
+      <c r="D268" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E268" s="3" t="inlineStr">
+        <is>
+          <t>Many sellers agree on part; equipment type not stated; current part is 24055</t>
         </is>
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="4" t="inlineStr">
+      <c r="A269" s="3" t="inlineStr">
         <is>
           <t>Gaylord</t>
         </is>
       </c>
-      <c r="B269" s="4" t="inlineStr">
+      <c r="B269" s="3" t="inlineStr">
         <is>
           <t>12828</t>
         </is>
       </c>
-      <c r="C269" s="4" t="inlineStr"/>
-      <c r="D269" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E269" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C269" s="3" t="inlineStr"/>
+      <c r="D269" s="3" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
+      <c r="E269" s="3" t="inlineStr">
+        <is>
+          <t>Searched "12828" Gaylord; only unrelated records (ZIP code, claims)</t>
         </is>
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="4" t="inlineStr">
+      <c r="A270" s="3" t="inlineStr">
         <is>
           <t>Gaylord</t>
         </is>
       </c>
-      <c r="B270" s="4" t="inlineStr">
+      <c r="B270" s="3" t="inlineStr">
         <is>
           <t>20527</t>
         </is>
       </c>
-      <c r="C270" s="4" t="inlineStr"/>
-      <c r="D270" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E270" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C270" s="3" t="inlineStr">
+        <is>
+          <t>Gaylord Operator Interface (C-7000) - 20527</t>
+        </is>
+      </c>
+      <c r="D270" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E270" s="3" t="inlineStr">
+        <is>
+          <t>Single seller plus Amazon; equipment type not stated</t>
         </is>
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="4" t="inlineStr">
+      <c r="A271" s="3" t="inlineStr">
         <is>
           <t>Gaylord</t>
         </is>
       </c>
-      <c r="B271" s="4" t="inlineStr">
+      <c r="B271" s="3" t="inlineStr">
         <is>
           <t>20883</t>
         </is>
       </c>
-      <c r="C271" s="4" t="inlineStr"/>
-      <c r="D271" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E271" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C271" s="3" t="inlineStr">
+        <is>
+          <t>Gaylord Control Board Power Supply 12VDC 25W - 20883</t>
+        </is>
+      </c>
+      <c r="D271" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E271" s="3" t="inlineStr">
+        <is>
+          <t>Parts Town and eBay; equipment type not stated</t>
         </is>
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="4" t="inlineStr">
+      <c r="A272" s="3" t="inlineStr">
         <is>
           <t>Gaylord</t>
         </is>
       </c>
-      <c r="B272" s="4" t="inlineStr">
+      <c r="B272" s="3" t="inlineStr">
         <is>
           <t>22454</t>
         </is>
       </c>
-      <c r="C272" s="4" t="inlineStr"/>
-      <c r="D272" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E272" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C272" s="3" t="inlineStr">
+        <is>
+          <t>Gaylord Optional Expansion Module (S2-S5) - 22454</t>
+        </is>
+      </c>
+      <c r="D272" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E272" s="3" t="inlineStr">
+        <is>
+          <t>Parts Town and eBay; equipment type not stated</t>
         </is>
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="4" t="inlineStr">
+      <c r="A273" t="inlineStr">
         <is>
           <t>Gaylord</t>
         </is>
       </c>
-      <c r="B273" s="4" t="inlineStr">
+      <c r="B273" t="inlineStr">
         <is>
           <t>30878</t>
         </is>
       </c>
-      <c r="C273" s="4" t="inlineStr"/>
-      <c r="D273" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E273" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Gaylord Exhaust Hood Sequential Control Kit (GRC-5000) - 30878</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Several sellers describe Gaylord kitchen exhaust hood system</t>
         </is>
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="4" t="inlineStr">
+      <c r="A274" t="inlineStr">
         <is>
           <t>GE</t>
         </is>
       </c>
-      <c r="B274" s="4" t="inlineStr">
+      <c r="B274" t="inlineStr">
         <is>
           <t>WR71X11046</t>
         </is>
       </c>
-      <c r="C274" s="4" t="inlineStr"/>
-      <c r="D274" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E274" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>GE Refrigerator Door Bin, Left Middle - WR71X11046</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Many sellers; description varies slightly (ice door bin)</t>
         </is>
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="4" t="inlineStr">
+      <c r="A275" s="2" t="inlineStr">
         <is>
           <t>Hvac Parts</t>
         </is>
       </c>
-      <c r="B275" s="4" t="inlineStr">
+      <c r="B275" s="2" t="inlineStr">
         <is>
           <t>1016380R</t>
         </is>
       </c>
-      <c r="C275" s="4" t="inlineStr"/>
-      <c r="D275" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E275" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>Hvac Parts Furnace Control Board, Single Stage (Nordyne) - 1016380R</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E275" s="2" t="inlineStr">
+        <is>
+          <t>Nordyne/Nortek PC board for B6/E4EB; brand given as Hvac Parts</t>
         </is>
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="4" t="inlineStr">
+      <c r="A276" s="2" t="inlineStr">
         <is>
           <t>Hvac Parts</t>
         </is>
       </c>
-      <c r="B276" s="4" t="inlineStr">
+      <c r="B276" s="2" t="inlineStr">
         <is>
           <t>96839</t>
         </is>
       </c>
-      <c r="C276" s="4" t="inlineStr"/>
-      <c r="D276" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E276" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C276" s="2" t="inlineStr">
+        <is>
+          <t>Hvac Parts Furnace Blower Wheel 10" x 9" x 1/2" Bore, CW - 96839</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E276" s="2" t="inlineStr">
+        <is>
+          <t>ICP/Heil/Tempstar furnaces; brand given as Hvac Parts</t>
         </is>
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="4" t="inlineStr">
+      <c r="A277" s="2" t="inlineStr">
         <is>
           <t>Garland</t>
         </is>
       </c>
-      <c r="B277" s="4" t="inlineStr">
+      <c r="B277" s="2" t="inlineStr">
         <is>
           <t>1360200</t>
         </is>
       </c>
-      <c r="C277" s="4" t="inlineStr"/>
-      <c r="D277" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E277" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C277" s="2" t="inlineStr">
+        <is>
+          <t>Garland Range BJWA Thermostat 100-450°F, 36" Capillary - 1360200</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E277" s="2" t="inlineStr">
+        <is>
+          <t>Sellers list G280/H280/P280 series grills and ranges</t>
         </is>
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="4" t="inlineStr">
+      <c r="A278" s="2" t="inlineStr">
         <is>
           <t>Garland</t>
         </is>
       </c>
-      <c r="B278" s="4" t="inlineStr">
+      <c r="B278" s="2" t="inlineStr">
         <is>
           <t>227005</t>
         </is>
       </c>
-      <c r="C278" s="4" t="inlineStr"/>
-      <c r="D278" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E278" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C278" s="2" t="inlineStr">
+        <is>
+          <t>Garland Range Burner Valve without Orifice - 227005</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E278" s="2" t="inlineStr">
+        <is>
+          <t>Sellers list GD/GTBG griddles and ranges</t>
         </is>
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="4" t="inlineStr">
+      <c r="A279" s="2" t="inlineStr">
         <is>
           <t>Garland</t>
         </is>
       </c>
-      <c r="B279" s="4" t="inlineStr">
+      <c r="B279" s="2" t="inlineStr">
         <is>
           <t>CKG7804-44</t>
         </is>
       </c>
-      <c r="C279" s="4" t="inlineStr"/>
-      <c r="D279" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E279" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C279" s="2" t="inlineStr">
+        <is>
+          <t>Garland Range Top Lighter Assembly Kit (Open Top Pilot) - CKG7804-44</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E279" s="2" t="inlineStr">
+        <is>
+          <t>Fit lists disagree (G280, G30 series)</t>
         </is>
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="4" t="inlineStr">
+      <c r="A280" t="inlineStr">
         <is>
           <t>Globe</t>
         </is>
       </c>
-      <c r="B280" s="4" t="inlineStr">
+      <c r="B280" t="inlineStr">
         <is>
           <t>330205-01</t>
         </is>
       </c>
-      <c r="C280" s="4" t="inlineStr"/>
-      <c r="D280" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E280" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Globe Slicer 13" Knife Cover Assembly - 330205-01</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Globe price list and sellers</t>
         </is>
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="4" t="inlineStr">
+      <c r="A281" s="2" t="inlineStr">
         <is>
           <t>Globe</t>
         </is>
       </c>
-      <c r="B281" s="4" t="inlineStr">
+      <c r="B281" s="2" t="inlineStr">
         <is>
           <t>349-A1</t>
         </is>
       </c>
-      <c r="C281" s="4" t="inlineStr"/>
-      <c r="D281" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E281" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C281" s="2" t="inlineStr">
+        <is>
+          <t>Globe Slicer Table Slide Guide Shim Kit - 349-A1</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E281" s="2" t="inlineStr">
+        <is>
+          <t>Parts Town and Good Earth; slicer type inferred from Globe</t>
         </is>
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="4" t="inlineStr">
+      <c r="A282" t="inlineStr">
         <is>
           <t>Globe</t>
         </is>
       </c>
-      <c r="B282" s="4" t="inlineStr">
+      <c r="B282" t="inlineStr">
         <is>
           <t>MCR76</t>
         </is>
       </c>
-      <c r="C282" s="4" t="inlineStr"/>
-      <c r="D282" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E282" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Globe Slicer Relay Socket - MCR76</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Globe G12/G14 slicer parts catalogs and sellers</t>
         </is>
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="4" t="inlineStr">
+      <c r="A283" s="2" t="inlineStr">
         <is>
           <t>Globe</t>
         </is>
       </c>
-      <c r="B283" s="4" t="inlineStr">
+      <c r="B283" s="2" t="inlineStr">
         <is>
           <t>VBEAT-60SS</t>
         </is>
       </c>
-      <c r="C283" s="4" t="inlineStr"/>
-      <c r="D283" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E283" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C283" s="2" t="inlineStr">
+        <is>
+          <t>Globe Mixer Stainless Steel Flat Beater (60 Qt) - VBEAT-60SS</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E283" s="2" t="inlineStr">
+        <is>
+          <t>Parts Town lists under Globe; eTundra lists it as a Varimixer part</t>
         </is>
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="4" t="inlineStr">
+      <c r="A284" t="inlineStr">
         <is>
           <t>Globe</t>
         </is>
       </c>
-      <c r="B284" s="4" t="inlineStr">
+      <c r="B284" t="inlineStr">
         <is>
           <t>X00676</t>
         </is>
       </c>
-      <c r="C284" s="4" t="inlineStr"/>
-      <c r="D284" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E284" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Globe Mixer Single Wire with Quick Connect (J5) - X00676</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Globe SP30/SP60 mixer parts manuals</t>
         </is>
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="4" t="inlineStr">
+      <c r="A285" s="2" t="inlineStr">
         <is>
           <t>Globe</t>
         </is>
       </c>
-      <c r="B285" s="4" t="inlineStr">
+      <c r="B285" s="2" t="inlineStr">
         <is>
           <t>X08160</t>
         </is>
       </c>
-      <c r="C285" s="4" t="inlineStr"/>
-      <c r="D285" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E285" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C285" s="2" t="inlineStr">
+        <is>
+          <t>Globe Mixer Digital Control Board Assembly (SP8) - X08160</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E285" s="2" t="inlineStr">
+        <is>
+          <t>Sellers fit SP8/SP08; -1 variant is a different part</t>
         </is>
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="4" t="inlineStr">
+      <c r="A286" s="2" t="inlineStr">
         <is>
           <t>Globe</t>
         </is>
       </c>
-      <c r="B286" s="4" t="inlineStr">
+      <c r="B286" s="2" t="inlineStr">
         <is>
           <t>X10006</t>
         </is>
       </c>
-      <c r="C286" s="4" t="inlineStr"/>
-      <c r="D286" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E286" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C286" s="2" t="inlineStr">
+        <is>
+          <t>Globe Mixer Hub Attachment, Dark Gray - X10006</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E286" s="2" t="inlineStr">
+        <is>
+          <t>Listed as X10006-DG; one seller lists a gasket under X10006</t>
         </is>
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="4" t="inlineStr">
+      <c r="A287" t="inlineStr">
         <is>
           <t>Globe</t>
         </is>
       </c>
-      <c r="B287" s="4" t="inlineStr">
+      <c r="B287" t="inlineStr">
         <is>
           <t>X40134-139</t>
         </is>
       </c>
-      <c r="C287" s="4" t="inlineStr"/>
-      <c r="D287" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E287" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Globe Mixer Shifter Yoke Assembly (SP40/SPC40) - X40134-139</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Globe price list and SP40E mixer parts catalog (gearbox item 39)</t>
         </is>
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="4" t="inlineStr">
+      <c r="A288" t="inlineStr">
         <is>
           <t>Groen</t>
         </is>
       </c>
-      <c r="B288" s="4" t="inlineStr">
+      <c r="B288" t="inlineStr">
         <is>
           <t>137487</t>
         </is>
       </c>
-      <c r="C288" s="4" t="inlineStr"/>
-      <c r="D288" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E288" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Groen Steam Kettle Transformer 20VA 120V Primary - 137487</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>Groen TDH manual and sellers</t>
         </is>
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="4" t="inlineStr">
+      <c r="A289" t="inlineStr">
         <is>
           <t>Groen</t>
         </is>
       </c>
-      <c r="B289" s="4" t="inlineStr">
+      <c r="B289" t="inlineStr">
         <is>
           <t>145660</t>
         </is>
       </c>
-      <c r="C289" s="4" t="inlineStr"/>
-      <c r="D289" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E289" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Groen Steam Kettle Power Tilt Motor Rectifier 208/240V - 145660</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Groen BPP/BPM parts manual and Parts Town</t>
         </is>
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="4" t="inlineStr">
+      <c r="A290" t="inlineStr">
         <is>
           <t>Groen</t>
         </is>
       </c>
-      <c r="B290" s="4" t="inlineStr">
+      <c r="B290" t="inlineStr">
         <is>
           <t>155489</t>
         </is>
       </c>
-      <c r="C290" s="4" t="inlineStr"/>
-      <c r="D290" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E290" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Groen Steamer Ignition Module (SSB 3/5/10G) - 155489</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Several sellers agree; some listings are aftermarket</t>
         </is>
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="4" t="inlineStr">
+      <c r="A291" s="2" t="inlineStr">
         <is>
           <t>Groen</t>
         </is>
       </c>
-      <c r="B291" s="4" t="inlineStr">
+      <c r="B291" s="2" t="inlineStr">
         <is>
           <t>Z002649S</t>
         </is>
       </c>
-      <c r="C291" s="4" t="inlineStr"/>
-      <c r="D291" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E291" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>Groen Steam Kettle Propane Gas Control Valve Kit - Z002649S</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="inlineStr">
+        <is>
+          <t>HFP/2 and BPM-30G fit lists differ; description varies</t>
         </is>
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="4" t="inlineStr">
+      <c r="A292" t="inlineStr">
         <is>
           <t>Groen</t>
         </is>
       </c>
-      <c r="B292" s="4" t="inlineStr">
+      <c r="B292" t="inlineStr">
         <is>
           <t>Z002845</t>
         </is>
       </c>
-      <c r="C292" s="4" t="inlineStr"/>
-      <c r="D292" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E292" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Groen Steam Kettle Sight Glass Fitting, 1/2" MPT (Pair) - Z002845</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Parts Town and BakeDeco list kettles EE-20/60/100, TDB</t>
         </is>
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="4" t="inlineStr">
+      <c r="A293" t="inlineStr">
         <is>
           <t>Groen</t>
         </is>
       </c>
-      <c r="B293" s="4" t="inlineStr">
+      <c r="B293" t="inlineStr">
         <is>
           <t>Z010412</t>
         </is>
       </c>
-      <c r="C293" s="4" t="inlineStr"/>
-      <c r="D293" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E293" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Groen Steam Kettle Low Water Cut-Off Relay 115V - Z010412</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Parts Town fit list DL/D40/HH kettles and skillets</t>
         </is>
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="4" t="inlineStr">
+      <c r="A294" s="2" t="inlineStr">
         <is>
           <t>Groen</t>
         </is>
       </c>
-      <c r="B294" s="4" t="inlineStr">
+      <c r="B294" s="2" t="inlineStr">
         <is>
           <t>Z013609</t>
         </is>
       </c>
-      <c r="C294" s="4" t="inlineStr"/>
-      <c r="D294" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E294" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C294" s="2" t="inlineStr">
+        <is>
+          <t>Groen Steam Kettle Gear, 3" Bore, 92 Teeth - Z013609</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E294" s="2" t="inlineStr">
+        <is>
+          <t>Parts Town DH series; sellers agree on the part</t>
         </is>
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="4" t="inlineStr">
+      <c r="A295" s="2" t="inlineStr">
         <is>
           <t>Groen</t>
         </is>
       </c>
-      <c r="B295" s="4" t="inlineStr">
+      <c r="B295" s="2" t="inlineStr">
         <is>
           <t>Z074839</t>
         </is>
       </c>
-      <c r="C295" s="4" t="inlineStr"/>
-      <c r="D295" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E295" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C295" s="2" t="inlineStr">
+        <is>
+          <t>Groen Braising Pan Transformer 120/208/240V - Z074839</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E295" s="2" t="inlineStr">
+        <is>
+          <t>CHFP/NHFP fit list; one seller lists 24V 20VA variant</t>
         </is>
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="4" t="inlineStr">
+      <c r="A296" s="2" t="inlineStr">
         <is>
           <t>Groen</t>
         </is>
       </c>
-      <c r="B296" s="4" t="inlineStr">
+      <c r="B296" s="2" t="inlineStr">
         <is>
           <t>Z079801</t>
         </is>
       </c>
-      <c r="C296" s="4" t="inlineStr"/>
-      <c r="D296" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E296" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C296" s="2" t="inlineStr">
+        <is>
+          <t>Groen Braising Pan Dual Solenoid Gas Valve 24V - Z079801</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E296" s="2" t="inlineStr">
+        <is>
+          <t>Fit models are braising pans; seller descriptions differ</t>
         </is>
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="4" t="inlineStr">
+      <c r="A297" t="inlineStr">
         <is>
           <t>Groen</t>
         </is>
       </c>
-      <c r="B297" s="4" t="inlineStr">
+      <c r="B297" t="inlineStr">
         <is>
           <t>Z079803</t>
         </is>
       </c>
-      <c r="C297" s="4" t="inlineStr"/>
-      <c r="D297" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E297" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Groen Steam Kettle Ignition Control 24V - Z079803</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Fits HH/4, HH/4E; many sellers</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="4" t="inlineStr">
+      <c r="A298" s="2" t="inlineStr">
         <is>
           <t>Groen</t>
         </is>
       </c>
-      <c r="B298" s="4" t="inlineStr">
+      <c r="B298" s="2" t="inlineStr">
         <is>
           <t>Z088260</t>
         </is>
       </c>
-      <c r="C298" s="4" t="inlineStr"/>
-      <c r="D298" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E298" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C298" s="2" t="inlineStr">
+        <is>
+          <t>Groen Steam Kettle Gas Valve 24V 60Hz Natural Gas (Basotrol) - Z088260</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E298" s="2" t="inlineStr">
+        <is>
+          <t>Parts Town and Webstaurant; no fit list</t>
         </is>
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="4" t="inlineStr">
+      <c r="A299" s="2" t="inlineStr">
         <is>
           <t>Groen</t>
         </is>
       </c>
-      <c r="B299" s="4" t="inlineStr">
+      <c r="B299" s="2" t="inlineStr">
         <is>
           <t>Z090827</t>
         </is>
       </c>
-      <c r="C299" s="4" t="inlineStr"/>
-      <c r="D299" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E299" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C299" s="2" t="inlineStr">
+        <is>
+          <t>Groen Steamer Water Inlet Solenoid Valve 3/4" In, 3/8" Out - Z090827</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E299" s="2" t="inlineStr">
+        <is>
+          <t>Fits HY/CC steamers; one variant has 1/2" hose</t>
         </is>
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="4" t="inlineStr">
+      <c r="A300" t="inlineStr">
         <is>
           <t>Groen</t>
         </is>
       </c>
-      <c r="B300" s="4" t="inlineStr">
+      <c r="B300" t="inlineStr">
         <is>
           <t>Z097001</t>
         </is>
       </c>
-      <c r="C300" s="4" t="inlineStr"/>
-      <c r="D300" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E300" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Groen Steam Kettle Gas Valve Kit 1/2" x 3/4" 120V - Z097001</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>HH/4 and HH/4E; many sellers</t>
         </is>
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="4" t="inlineStr">
+      <c r="A301" s="3" t="inlineStr">
         <is>
           <t>Hatco</t>
         </is>
       </c>
-      <c r="B301" s="4" t="inlineStr">
+      <c r="B301" s="3" t="inlineStr">
         <is>
           <t>02.19.193.00</t>
         </is>
       </c>
-      <c r="C301" s="4" t="inlineStr"/>
-      <c r="D301" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E301" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C301" s="3" t="inlineStr">
+        <is>
+          <t>Hatco DPDT Micro Safety Switch 20A - 02.19.193.00</t>
+        </is>
+      </c>
+      <c r="D301" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E301" s="3" t="inlineStr">
+        <is>
+          <t>Parts Town fit list is TPT models; equipment type not confirmed</t>
         </is>
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="4" t="inlineStr">
+      <c r="A302" t="inlineStr">
         <is>
           <t>Hatco</t>
         </is>
       </c>
-      <c r="B302" s="4" t="inlineStr">
+      <c r="B302" t="inlineStr">
         <is>
           <t>02.30.097.00</t>
         </is>
       </c>
-      <c r="C302" s="4" t="inlineStr"/>
-      <c r="D302" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E302" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Hatco Heat Lamp Infrared Bulb 375W Clear Coated - 02.30.097.00</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Fits DL-800/1200/2300; voltage listed 120V vs 125V</t>
         </is>
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="4" t="inlineStr">
+      <c r="A303" t="inlineStr">
         <is>
           <t>Hatco</t>
         </is>
       </c>
-      <c r="B303" s="4" t="inlineStr">
+      <c r="B303" t="inlineStr">
         <is>
           <t>R02.01.212.00</t>
         </is>
       </c>
-      <c r="C303" s="4" t="inlineStr"/>
-      <c r="D303" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E303" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Hatco Rethermalizer Low Water Cut-Off Board 24V with Delay - R02.01.212.00</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>FFR2 hydro-heaters; one eBay listing conflicts</t>
         </is>
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="4" t="inlineStr">
+      <c r="A304" s="2" t="inlineStr">
         <is>
           <t>Hatco</t>
         </is>
       </c>
-      <c r="B304" s="4" t="inlineStr">
+      <c r="B304" s="2" t="inlineStr">
         <is>
           <t>R02.12.001.00</t>
         </is>
       </c>
-      <c r="C304" s="4" t="inlineStr"/>
-      <c r="D304" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E304" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C304" s="2" t="inlineStr">
+        <is>
+          <t>Hatco Food Warmer Blower Motor &amp; Cord Kit 120V - R02.12.001.00</t>
+        </is>
+      </c>
+      <c r="D304" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E304" s="2" t="inlineStr">
+        <is>
+          <t>Hatco Flav-R-Savor parts list; sellers split 115V vs 120V</t>
         </is>
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="4" t="inlineStr">
+      <c r="A305" s="2" t="inlineStr">
         <is>
           <t>Hatco</t>
         </is>
       </c>
-      <c r="B305" s="4" t="inlineStr">
+      <c r="B305" s="2" t="inlineStr">
         <is>
           <t>R02.13.111.00</t>
         </is>
       </c>
-      <c r="C305" s="4" t="inlineStr"/>
-      <c r="D305" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E305" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C305" s="2" t="inlineStr">
+        <is>
+          <t>Hatco Toaster Speed Control Rheostat Kit 200 Ohm 25W - R02.13.111.00</t>
+        </is>
+      </c>
+      <c r="D305" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E305" s="2" t="inlineStr">
+        <is>
+          <t>Fits TK/TQ toasters; specs differ across sellers</t>
         </is>
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="4" t="inlineStr">
+      <c r="A306" t="inlineStr">
         <is>
           <t>Hatco</t>
         </is>
       </c>
-      <c r="B306" s="4" t="inlineStr">
+      <c r="B306" t="inlineStr">
         <is>
           <t>R02.19.019.00</t>
         </is>
       </c>
-      <c r="C306" s="4" t="inlineStr"/>
-      <c r="D306" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E306" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Hatco Food Warmer Infinite Switch Kit 240V 13A - R02.19.019.00</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Hatco Glo-Ray parts lists</t>
         </is>
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="4" t="inlineStr">
+      <c r="A307" s="2" t="inlineStr">
         <is>
           <t>Hatco</t>
         </is>
       </c>
-      <c r="B307" s="4" t="inlineStr">
+      <c r="B307" s="2" t="inlineStr">
         <is>
           <t>R04.17.328.00</t>
         </is>
       </c>
-      <c r="C307" s="4" t="inlineStr"/>
-      <c r="D307" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E307" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C307" s="2" t="inlineStr">
+        <is>
+          <t>Hatco Chip Warmer Stainless Steel Upper Door Kit - R04.17.328.00</t>
+        </is>
+      </c>
+      <c r="D307" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E307" s="2" t="inlineStr">
+        <is>
+          <t>Listed for FST-1-MN Macho Nacho warmer</t>
         </is>
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="4" t="inlineStr">
+      <c r="A308" s="2" t="inlineStr">
         <is>
           <t>Heatcraft</t>
         </is>
       </c>
-      <c r="B308" s="4" t="inlineStr">
+      <c r="B308" s="2" t="inlineStr">
         <is>
           <t>20903</t>
         </is>
       </c>
-      <c r="C308" s="4" t="inlineStr"/>
-      <c r="D308" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E308" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C308" s="2" t="inlineStr">
+        <is>
+          <t>Heatcraft Low Temp &amp; Manual Defrost Controller Assembly (KE2Therm) - 20903</t>
+        </is>
+      </c>
+      <c r="D308" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E308" s="2" t="inlineStr">
+        <is>
+          <t>Many sellers; refrigeration/HVAC controller, equipment type not stated</t>
         </is>
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="4" t="inlineStr">
+      <c r="A309" s="2" t="inlineStr">
         <is>
           <t>Hisense</t>
         </is>
       </c>
-      <c r="B309" s="4" t="inlineStr">
+      <c r="B309" s="2" t="inlineStr">
         <is>
           <t>K1430814</t>
         </is>
       </c>
-      <c r="C309" s="4" t="inlineStr"/>
-      <c r="D309" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E309" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C309" s="2" t="inlineStr">
+        <is>
+          <t>Hisense Refrigerator Fresh Food Temperature Sensor - K1430814</t>
+        </is>
+      </c>
+      <c r="D309" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E309" s="2" t="inlineStr">
+        <is>
+          <t>Listed for HQD20058SV/HRF254N6; also Gorenje-branded</t>
         </is>
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="4" t="inlineStr">
+      <c r="A310" t="inlineStr">
         <is>
           <t>Henny Penny</t>
         </is>
       </c>
-      <c r="B310" s="4" t="inlineStr">
+      <c r="B310" t="inlineStr">
         <is>
           <t>BL01-018</t>
         </is>
       </c>
-      <c r="C310" s="4" t="inlineStr"/>
-      <c r="D310" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E310" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Henny Penny Holding Cabinet Halogen Lamp 90W 120V - BL01-018</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Fits HDS-300, HMR-104, HMR-125 warmers</t>
         </is>
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="4" t="inlineStr">
+      <c r="A311" t="inlineStr">
         <is>
           <t>Hobart</t>
         </is>
       </c>
-      <c r="B311" s="4" t="inlineStr">
+      <c r="B311" t="inlineStr">
         <is>
           <t>00-046642</t>
         </is>
       </c>
-      <c r="C311" s="4" t="inlineStr"/>
-      <c r="D311" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E311" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Hobart Wrapping Station Film Retainer Rod 1/4" x 22-5/8" - 00-046642</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Hobart 625A/W32 parts catalog</t>
         </is>
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="4" t="inlineStr">
+      <c r="A312" t="inlineStr">
         <is>
           <t>Hobart</t>
         </is>
       </c>
-      <c r="B312" s="4" t="inlineStr">
+      <c r="B312" t="inlineStr">
         <is>
           <t>00-074868-00001</t>
         </is>
       </c>
-      <c r="C312" s="4" t="inlineStr"/>
-      <c r="D312" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E312" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Hobart Slicer Upper Hinge Pin (VS9) - 00-074868-00001</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Hobart VS9 parts catalog and sellers</t>
         </is>
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="4" t="inlineStr">
+      <c r="A313" s="3" t="inlineStr">
         <is>
           <t>Hobart</t>
         </is>
       </c>
-      <c r="B313" s="4" t="inlineStr">
+      <c r="B313" s="3" t="inlineStr">
         <is>
           <t>00-087713-040-1</t>
         </is>
       </c>
-      <c r="C313" s="4" t="inlineStr"/>
-      <c r="D313" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E313" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C313" s="3" t="inlineStr">
+        <is>
+          <t>Hobart Contactor 30A 3-Pole 220V Coil - 00-087713-040-1</t>
+        </is>
+      </c>
+      <c r="D313" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E313" s="3" t="inlineStr">
+        <is>
+          <t>Many sellers agree; used across Hobart cutters/ovens/dishwashers, no single type</t>
         </is>
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="4" t="inlineStr">
+      <c r="A314" s="2" t="inlineStr">
         <is>
           <t>Hobart</t>
         </is>
       </c>
-      <c r="B314" s="4" t="inlineStr">
+      <c r="B314" s="2" t="inlineStr">
         <is>
           <t>00-087713-102-1</t>
         </is>
       </c>
-      <c r="C314" s="4" t="inlineStr"/>
-      <c r="D314" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E314" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>Hobart Meat Saw Contactor 3-Pole 30A with Aux Switch - 00-087713-102-1</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="inlineStr">
+        <is>
+          <t>Parts Town lists under meat saws 6614/6801</t>
         </is>
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="4" t="inlineStr">
+      <c r="A315" t="inlineStr">
         <is>
           <t>Hobart</t>
         </is>
       </c>
-      <c r="B315" s="4" t="inlineStr">
+      <c r="B315" t="inlineStr">
         <is>
           <t>00-293856</t>
         </is>
       </c>
-      <c r="C315" s="4" t="inlineStr"/>
-      <c r="D315" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E315" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Hobart Dishwasher Wash Arm Plug, White - 00-293856</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Fits FT800/FTM800</t>
         </is>
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="4" t="inlineStr">
+      <c r="A316" s="2" t="inlineStr">
         <is>
           <t>Hobart</t>
         </is>
       </c>
-      <c r="B316" s="4" t="inlineStr">
+      <c r="B316" s="2" t="inlineStr">
         <is>
           <t>00-295597</t>
         </is>
       </c>
-      <c r="C316" s="4" t="inlineStr"/>
-      <c r="D316" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E316" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>Hobart Meat Saw 3-Phase Power Cord &amp; Plug Assembly - 00-295597</t>
+        </is>
+      </c>
+      <c r="D316" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E316" s="2" t="inlineStr">
+        <is>
+          <t>Hobart 6614/6801 parts manuals; no retailer listing</t>
         </is>
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="4" t="inlineStr">
+      <c r="A317" t="inlineStr">
         <is>
           <t>Hobart</t>
         </is>
       </c>
-      <c r="B317" s="4" t="inlineStr">
+      <c r="B317" t="inlineStr">
         <is>
           <t>00-421905-000G1</t>
         </is>
       </c>
-      <c r="C317" s="4" t="inlineStr"/>
-      <c r="D317" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E317" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Hobart Convection Oven Right Hand Door Frame Assembly - 00-421905-000G1</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Hobart DGC5/HGC5 parts manual and sellers</t>
         </is>
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="4" t="inlineStr">
+      <c r="A318" t="inlineStr">
         <is>
           <t>Hobart</t>
         </is>
       </c>
-      <c r="B318" s="4" t="inlineStr">
+      <c r="B318" t="inlineStr">
         <is>
           <t>00-562895-00001</t>
         </is>
       </c>
-      <c r="C318" s="4" t="inlineStr"/>
-      <c r="D318" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E318" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Hobart Dishwasher Terminal Block 3-Pole 40A - 00-562895-00001</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Hobart AM16 manual and sellers</t>
         </is>
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="4" t="inlineStr">
+      <c r="A319" t="inlineStr">
         <is>
           <t>Hobart</t>
         </is>
       </c>
-      <c r="B319" s="4" t="inlineStr">
+      <c r="B319" t="inlineStr">
         <is>
           <t>00-563780</t>
         </is>
       </c>
-      <c r="C319" s="4" t="inlineStr"/>
-      <c r="D319" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E319" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Hobart Dishwasher Electric Booster Tank Kit (LXN to LXE) - 00-563780</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Undercounter LXE; many sellers</t>
         </is>
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="4" t="inlineStr">
+      <c r="A320" s="2" t="inlineStr">
         <is>
           <t>Hobart</t>
         </is>
       </c>
-      <c r="B320" s="4" t="inlineStr">
+      <c r="B320" s="2" t="inlineStr">
         <is>
           <t>00-875632</t>
         </is>
       </c>
-      <c r="C320" s="4" t="inlineStr"/>
-      <c r="D320" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E320" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>Hobart Food Processor Link Sleeve (FP250) - 00-875632</t>
+        </is>
+      </c>
+      <c r="D320" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E320" s="2" t="inlineStr">
+        <is>
+          <t>eBay and Berkel Sales listings</t>
         </is>
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="4" t="inlineStr">
+      <c r="A321" s="2" t="inlineStr">
         <is>
           <t>Hobart</t>
         </is>
       </c>
-      <c r="B321" s="4" t="inlineStr">
+      <c r="B321" s="2" t="inlineStr">
         <is>
           <t>00-875638</t>
         </is>
       </c>
-      <c r="C321" s="4" t="inlineStr"/>
-      <c r="D321" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E321" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>Hobart Food Processor Guide Bushing (FP250) - 00-875638</t>
+        </is>
+      </c>
+      <c r="D321" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E321" s="2" t="inlineStr">
+        <is>
+          <t>Hobart FP250 parts manual and one reseller</t>
         </is>
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="4" t="inlineStr">
+      <c r="A322" s="3" t="inlineStr">
         <is>
           <t>Hobart</t>
         </is>
       </c>
-      <c r="B322" s="4" t="inlineStr">
+      <c r="B322" s="3" t="inlineStr">
         <is>
           <t>00-892543-00002</t>
         </is>
       </c>
-      <c r="C322" s="4" t="inlineStr"/>
-      <c r="D322" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E322" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C322" s="3" t="inlineStr"/>
+      <c r="D322" s="3" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
+      <c r="E322" s="3" t="inlineStr">
+        <is>
+          <t>Searched "00-892543-00002" Hobart; no listing mentions this number</t>
         </is>
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="4" t="inlineStr">
+      <c r="A323" t="inlineStr">
         <is>
           <t>Hobart</t>
         </is>
       </c>
-      <c r="B323" s="4" t="inlineStr">
+      <c r="B323" t="inlineStr">
         <is>
           <t>00-915257</t>
         </is>
       </c>
-      <c r="C323" s="4" t="inlineStr"/>
-      <c r="D323" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E323" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Hobart Slicer Product Feed Grip (HS Series) - 00-915257</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>Listed as 00-915257-00002; several sellers agree</t>
         </is>
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="4" t="inlineStr">
+      <c r="A324" s="2" t="inlineStr">
         <is>
           <t>Hobart</t>
         </is>
       </c>
-      <c r="B324" s="4" t="inlineStr">
+      <c r="B324" s="2" t="inlineStr">
         <is>
           <t>00-915532</t>
         </is>
       </c>
-      <c r="C324" s="4" t="inlineStr"/>
-      <c r="D324" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E324" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>Hobart Food Processor Slicer Plate 4mm (5/32") - 00-915532</t>
+        </is>
+      </c>
+      <c r="D324" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E324" s="2" t="inlineStr">
+        <is>
+          <t>Sellers say FP100 / HCC34; wording varies</t>
         </is>
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="4" t="inlineStr">
+      <c r="A325" s="2" t="inlineStr">
         <is>
           <t>Hobart</t>
         </is>
       </c>
-      <c r="B325" s="4" t="inlineStr">
+      <c r="B325" s="2" t="inlineStr">
         <is>
           <t>00-915926</t>
         </is>
       </c>
-      <c r="C325" s="4" t="inlineStr"/>
-      <c r="D325" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E325" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t>Hobart Slicer Slicer Deflector - 00-915926</t>
+        </is>
+      </c>
+      <c r="D325" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E325" s="2" t="inlineStr">
+        <is>
+          <t>Hobart EDGE 13-11 parts catalog and AllPoints</t>
         </is>
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="4" t="inlineStr">
+      <c r="A326" t="inlineStr">
         <is>
           <t>Hobart</t>
         </is>
       </c>
-      <c r="B326" s="4" t="inlineStr">
+      <c r="B326" t="inlineStr">
         <is>
           <t>00-919978-00005</t>
         </is>
       </c>
-      <c r="C326" s="4" t="inlineStr"/>
-      <c r="D326" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E326" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Hobart Dishwasher Conveyor Drive Gearmotor 200-230V 3PH (CL54e) - 00-919978-00005</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Hobart CL44e/CL54e parts catalog and sellers</t>
         </is>
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="4" t="inlineStr">
+      <c r="A327" s="2" t="inlineStr">
         <is>
           <t>Hobart</t>
         </is>
       </c>
-      <c r="B327" s="4" t="inlineStr">
+      <c r="B327" s="2" t="inlineStr">
         <is>
           <t>00-919978-00009</t>
         </is>
       </c>
-      <c r="C327" s="4" t="inlineStr"/>
-      <c r="D327" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E327" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>Hobart Dishwasher Conveyor Drive Motor 200-230/460V 3PH - 00-919978-00009</t>
+        </is>
+      </c>
+      <c r="D327" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E327" s="2" t="inlineStr">
+        <is>
+          <t>Many sellers; fit to CL series inferred from sibling part number</t>
         </is>
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="4" t="inlineStr">
+      <c r="A328" t="inlineStr">
         <is>
           <t>Hobart</t>
         </is>
       </c>
-      <c r="B328" s="4" t="inlineStr">
+      <c r="B328" t="inlineStr">
         <is>
           <t>00-936168</t>
         </is>
       </c>
-      <c r="C328" s="4" t="inlineStr"/>
-      <c r="D328" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E328" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Hobart Dishwasher Wash Arm Adjuster Plate - 00-936168</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Hobart CLPS66e parts list and sellers</t>
         </is>
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="4" t="inlineStr">
+      <c r="A329" s="3" t="inlineStr">
         <is>
           <t>Hobart</t>
         </is>
       </c>
-      <c r="B329" s="4" t="inlineStr">
+      <c r="B329" s="3" t="inlineStr">
         <is>
           <t>00-937329-00003</t>
         </is>
       </c>
-      <c r="C329" s="4" t="inlineStr"/>
-      <c r="D329" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E329" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C329" s="3" t="inlineStr"/>
+      <c r="D329" s="3" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
+      <c r="E329" s="3" t="inlineStr">
+        <is>
+          <t>Results mention a seal for HL120/200 mixers but name different part numbers (e.g. 00-874512-00003); exact number not confirmed</t>
         </is>
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="4" t="inlineStr">
+      <c r="A330" t="inlineStr">
         <is>
           <t>Hobart</t>
         </is>
       </c>
-      <c r="B330" s="4" t="inlineStr">
+      <c r="B330" t="inlineStr">
         <is>
           <t>00-949651-00002</t>
         </is>
       </c>
-      <c r="C330" s="4" t="inlineStr"/>
-      <c r="D330" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E330" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Hobart Dishwasher P-Pump Service Hose Kit (PW 8.0") - 00-949651-00002</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Fits FT1000S, PWVeR; several sellers</t>
         </is>
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="4" t="inlineStr">
+      <c r="A331" s="2" t="inlineStr">
         <is>
           <t>Hobart</t>
         </is>
       </c>
-      <c r="B331" s="4" t="inlineStr">
+      <c r="B331" s="2" t="inlineStr">
         <is>
           <t>00-962067-0KIT1</t>
         </is>
       </c>
-      <c r="C331" s="4" t="inlineStr"/>
-      <c r="D331" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E331" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>Hobart Range Safety Valve Service Kit - 00-962067-0KIT1</t>
+        </is>
+      </c>
+      <c r="D331" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E331" s="2" t="inlineStr">
+        <is>
+          <t>Sold under Hobart and Vulcan names; heavy-duty ranges per Vulcan listing</t>
         </is>
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="4" t="inlineStr">
+      <c r="A332" s="2" t="inlineStr">
         <is>
           <t>Hobart</t>
         </is>
       </c>
-      <c r="B332" s="4" t="inlineStr">
+      <c r="B332" s="2" t="inlineStr">
         <is>
           <t>00-975443-00001</t>
         </is>
       </c>
-      <c r="C332" s="4" t="inlineStr"/>
-      <c r="D332" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E332" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>Hobart Prep Washer HMI Display - 00-975443-00001</t>
+        </is>
+      </c>
+      <c r="D332" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E332" s="2" t="inlineStr">
+        <is>
+          <t>Parts Town and PW-series parts catalog</t>
         </is>
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="4" t="inlineStr">
+      <c r="A333" s="2" t="inlineStr">
         <is>
           <t>Hobart</t>
         </is>
       </c>
-      <c r="B333" s="4" t="inlineStr">
+      <c r="B333" s="2" t="inlineStr">
         <is>
           <t>00-978900-30002</t>
         </is>
       </c>
-      <c r="C333" s="4" t="inlineStr"/>
-      <c r="D333" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E333" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C333" s="2" t="inlineStr">
+        <is>
+          <t>Hobart Convection Oven Spark Ignitor/Sensor (OV500G) - 00-978900-30002</t>
+        </is>
+      </c>
+      <c r="D333" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E333" s="2" t="inlineStr">
+        <is>
+          <t>Single seller (Parts Town) plus Schedule73</t>
         </is>
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="4" t="inlineStr">
+      <c r="A334" s="3" t="inlineStr">
         <is>
           <t>Hobart</t>
         </is>
       </c>
-      <c r="B334" s="4" t="inlineStr">
+      <c r="B334" s="3" t="inlineStr">
         <is>
           <t>FP-090-91</t>
         </is>
       </c>
-      <c r="C334" s="4" t="inlineStr"/>
-      <c r="D334" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E334" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C334" s="3" t="inlineStr"/>
+      <c r="D334" s="3" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
+      <c r="E334" s="3" t="inlineStr">
+        <is>
+          <t>Searched "FP-090-91" Hobart; no listing found (only neighbouring FP-091-66)</t>
         </is>
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="4" t="inlineStr">
+      <c r="A335" s="3" t="inlineStr">
         <is>
           <t>Hobart</t>
         </is>
       </c>
-      <c r="B335" s="4" t="inlineStr">
+      <c r="B335" s="3" t="inlineStr">
         <is>
           <t>SC-121-72</t>
         </is>
       </c>
-      <c r="C335" s="4" t="inlineStr"/>
-      <c r="D335" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E335" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C335" s="3" t="inlineStr">
+        <is>
+          <t>Hobart Machine Screw, Button Head 1/4-20 x 1/2" - SC-121-72</t>
+        </is>
+      </c>
+      <c r="D335" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E335" s="3" t="inlineStr">
+        <is>
+          <t>Sellers agree on part; fits several Hobart machine types</t>
         </is>
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="4" t="inlineStr">
+      <c r="A336" t="inlineStr">
         <is>
           <t>Ge</t>
         </is>
       </c>
-      <c r="B336" s="4" t="inlineStr">
+      <c r="B336" t="inlineStr">
         <is>
           <t>WR14X27234</t>
         </is>
       </c>
-      <c r="C336" s="4" t="inlineStr"/>
-      <c r="D336" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E336" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Ge Refrigerator Freezer Door Gasket - WR14X27234</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Many sellers agree; some report discontinued</t>
         </is>
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="4" t="inlineStr">
+      <c r="A337" t="inlineStr">
         <is>
           <t>Ice-O-Matic</t>
         </is>
       </c>
-      <c r="B337" s="4" t="inlineStr">
+      <c r="B337" t="inlineStr">
         <is>
           <t>1011337-31</t>
         </is>
       </c>
-      <c r="C337" s="4" t="inlineStr"/>
-      <c r="D337" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E337" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Ice-O-Matic Ice Machine Water Pump 115V - 1011337-31</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>ICEU070A manual and sellers</t>
         </is>
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="4" t="inlineStr">
+      <c r="A338" s="2" t="inlineStr">
         <is>
           <t>Ice-O-Matic</t>
         </is>
       </c>
-      <c r="B338" s="4" t="inlineStr">
+      <c r="B338" s="2" t="inlineStr">
         <is>
           <t>1011448-115</t>
         </is>
       </c>
-      <c r="C338" s="4" t="inlineStr"/>
-      <c r="D338" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E338" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>Ice-O-Matic Ice Machine Drier - 1011448-115</t>
+        </is>
+      </c>
+      <c r="D338" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E338" s="2" t="inlineStr">
+        <is>
+          <t>Ice-O-Matic price list and FixIce; no fit model</t>
         </is>
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="4" t="inlineStr">
+      <c r="A339" s="2" t="inlineStr">
         <is>
           <t>Ice-O-Matic</t>
         </is>
       </c>
-      <c r="B339" s="4" t="inlineStr">
+      <c r="B339" s="2" t="inlineStr">
         <is>
           <t>1011517-10</t>
         </is>
       </c>
-      <c r="C339" s="4" t="inlineStr"/>
-      <c r="D339" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E339" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>Ice-O-Matic Ice Machine Inspection Window - 1011517-10</t>
+        </is>
+      </c>
+      <c r="D339" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="inlineStr">
+        <is>
+          <t>Sellers split window vs sliding inspection door</t>
         </is>
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="4" t="inlineStr">
+      <c r="A340" s="2" t="inlineStr">
         <is>
           <t>Ice-O-Matic</t>
         </is>
       </c>
-      <c r="B340" s="4" t="inlineStr">
+      <c r="B340" s="2" t="inlineStr">
         <is>
           <t>9051237-01</t>
         </is>
       </c>
-      <c r="C340" s="4" t="inlineStr"/>
-      <c r="D340" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E340" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>Ice-O-Matic Ice Machine Washer Tube - 9051237-01</t>
+        </is>
+      </c>
+      <c r="D340" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E340" s="2" t="inlineStr">
+        <is>
+          <t>ICE1506 service parts and one retailer</t>
         </is>
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="4" t="inlineStr">
+      <c r="A341" t="inlineStr">
         <is>
           <t>Ice-O-Matic</t>
         </is>
       </c>
-      <c r="B341" s="4" t="inlineStr">
+      <c r="B341" t="inlineStr">
         <is>
           <t>9051638-01</t>
         </is>
       </c>
-      <c r="C341" s="4" t="inlineStr"/>
-      <c r="D341" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E341" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Ice-O-Matic Ice Machine Slotted Collar - 9051638-01</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>Ice-O-Matic GEM/MFI service parts manual and retailers</t>
         </is>
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="4" t="inlineStr">
+      <c r="A342" t="inlineStr">
         <is>
           <t>Ice-O-Matic</t>
         </is>
       </c>
-      <c r="B342" s="4" t="inlineStr">
+      <c r="B342" t="inlineStr">
         <is>
           <t>9091074-01</t>
         </is>
       </c>
-      <c r="C342" s="4" t="inlineStr"/>
-      <c r="D342" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E342" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Ice-O-Matic Ice Machine Water Inlet Drop Adapter Fitting 3/8" FPT - 9091074-01</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Parts Town, Gulf Ice and Ice-O-Matic parts PDF</t>
         </is>
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="4" t="inlineStr">
+      <c r="A343" t="inlineStr">
         <is>
           <t>Ice-O-Matic</t>
         </is>
       </c>
-      <c r="B343" s="4" t="inlineStr">
+      <c r="B343" t="inlineStr">
         <is>
           <t>9151163-01</t>
         </is>
       </c>
-      <c r="C343" s="4" t="inlineStr"/>
-      <c r="D343" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E343" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Ice-O-Matic Ice Machine Filter/Drier (EK-032S) - 9151163-01</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Parts Town and several sellers</t>
         </is>
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="4" t="inlineStr">
+      <c r="A344" t="inlineStr">
         <is>
           <t>Ice-O-Matic</t>
         </is>
       </c>
-      <c r="B344" s="4" t="inlineStr">
+      <c r="B344" t="inlineStr">
         <is>
           <t>9151163-02</t>
         </is>
       </c>
-      <c r="C344" s="4" t="inlineStr"/>
-      <c r="D344" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E344" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Ice-O-Matic Ice Machine Filter/Drier (EK083S) - 9151163-02</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Ice-O-Matic ICE1806/1807 parts manual and sellers</t>
         </is>
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="4" t="inlineStr">
+      <c r="A345" t="inlineStr">
         <is>
           <t>Ice-O-Matic</t>
         </is>
       </c>
-      <c r="B345" s="4" t="inlineStr">
+      <c r="B345" t="inlineStr">
         <is>
           <t>IFQ1</t>
         </is>
       </c>
-      <c r="C345" s="4" t="inlineStr"/>
-      <c r="D345" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E345" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Ice-O-Matic Ice Machine Single Water Filtration System - IFQ1</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Many sellers agree</t>
         </is>
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="4" t="inlineStr">
+      <c r="A346" s="2" t="inlineStr">
         <is>
           <t>Int. Confort Parts</t>
         </is>
       </c>
-      <c r="B346" s="4" t="inlineStr">
+      <c r="B346" s="2" t="inlineStr">
         <is>
           <t>H-NT08</t>
         </is>
       </c>
-      <c r="C346" s="4" t="inlineStr"/>
-      <c r="D346" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E346" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>Int. Confort Parts Odor Neutralizer HydroBalance Neutronic Gel 1/2 lb - H-NT08</t>
+        </is>
+      </c>
+      <c r="D346" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E346" s="2" t="inlineStr">
+        <is>
+          <t>HVAC odor gel; listed under ICP parts, not an ICP-made part</t>
         </is>
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="4" t="inlineStr">
+      <c r="A347" s="2" t="inlineStr">
         <is>
           <t>Intl Enviormental Co</t>
         </is>
       </c>
-      <c r="B347" s="4" t="inlineStr">
+      <c r="B347" s="2" t="inlineStr">
         <is>
           <t>E005-70300201</t>
         </is>
       </c>
-      <c r="C347" s="4" t="inlineStr"/>
-      <c r="D347" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E347" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>Intl Enviormental Co Fan Coil Electric Strip Heater 277V 3.0kW - E005-70300201</t>
+        </is>
+      </c>
+      <c r="D347" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E347" s="2" t="inlineStr">
+        <is>
+          <t>Parts Town and retailers; discontinued</t>
         </is>
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="4" t="inlineStr">
+      <c r="A348" s="2" t="inlineStr">
         <is>
           <t>Intl Enviormental Co</t>
         </is>
       </c>
-      <c r="B348" s="4" t="inlineStr">
+      <c r="B348" s="2" t="inlineStr">
         <is>
           <t>E020-70556314</t>
         </is>
       </c>
-      <c r="C348" s="4" t="inlineStr"/>
-      <c r="D348" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E348" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>Intl Enviormental Co Fan Coil Direct Drive Motor 1/20 HP 208-230V - E020-70556314</t>
+        </is>
+      </c>
+      <c r="D348" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E348" s="2" t="inlineStr">
+        <is>
+          <t>Parts Town, AllPoints; MUY/MMY fan coil series</t>
         </is>
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="4" t="inlineStr">
+      <c r="A349" s="2" t="inlineStr">
         <is>
           <t>Lennox</t>
         </is>
       </c>
-      <c r="B349" s="4" t="inlineStr">
+      <c r="B349" s="2" t="inlineStr">
         <is>
           <t>Y5419</t>
         </is>
       </c>
-      <c r="C349" s="4" t="inlineStr"/>
-      <c r="D349" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E349" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C349" s="2" t="inlineStr">
+        <is>
+          <t>Lennox Mini Split Axial Bushing (LMS) - Y5419</t>
+        </is>
+      </c>
+      <c r="D349" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E349" s="2" t="inlineStr">
+        <is>
+          <t>Single Lennox Pros catalog page</t>
         </is>
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="4" t="inlineStr">
+      <c r="A350" s="2" t="inlineStr">
         <is>
           <t>Lennox</t>
         </is>
       </c>
-      <c r="B350" s="4" t="inlineStr">
+      <c r="B350" s="2" t="inlineStr">
         <is>
           <t>14U47</t>
         </is>
       </c>
-      <c r="C350" s="4" t="inlineStr"/>
-      <c r="D350" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E350" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>Lennox Air Conditioner Panel Louver Center 24x28 - 14U47</t>
+        </is>
+      </c>
+      <c r="D350" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E350" s="2" t="inlineStr">
+        <is>
+          <t>Retailer listings; ML13/ML14 condensers</t>
         </is>
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="4" t="inlineStr">
+      <c r="A351" s="2" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="B351" s="4" t="inlineStr">
+      <c r="B351" s="2" t="inlineStr">
         <is>
           <t>AEB74684603</t>
         </is>
       </c>
-      <c r="C351" s="4" t="inlineStr"/>
-      <c r="D351" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E351" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C351" s="2" t="inlineStr">
+        <is>
+          <t>LG Range Grille Assembly - AEB74684603</t>
+        </is>
+      </c>
+      <c r="D351" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E351" s="2" t="inlineStr">
+        <is>
+          <t>Parts-list listings only, limited detail</t>
         </is>
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="4" t="inlineStr">
+      <c r="A352" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="B352" s="4" t="inlineStr">
+      <c r="B352" t="inlineStr">
         <is>
           <t>AGL75675225</t>
         </is>
       </c>
-      <c r="C352" s="4" t="inlineStr"/>
-      <c r="D352" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E352" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>LG Dishwasher Control Panel Assembly - AGL75675225</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Many sellers agree</t>
         </is>
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="4" t="inlineStr">
+      <c r="A353" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="B353" s="4" t="inlineStr">
+      <c r="B353" t="inlineStr">
         <is>
           <t>AJK72989704</t>
         </is>
       </c>
-      <c r="C353" s="4" t="inlineStr"/>
-      <c r="D353" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E353" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>LG Washer Suspension Rod Assembly (Set of 4) - AJK72989704</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Many sellers agree</t>
         </is>
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="4" t="inlineStr">
+      <c r="A354" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="B354" s="4" t="inlineStr">
+      <c r="B354" t="inlineStr">
         <is>
           <t>EBR79686302</t>
         </is>
       </c>
-      <c r="C354" s="4" t="inlineStr"/>
-      <c r="D354" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E354" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>LG Dishwasher Main Control Board - EBR79686302</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Many sellers agree</t>
         </is>
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="4" t="inlineStr">
+      <c r="A355" s="2" t="inlineStr">
         <is>
           <t>LG</t>
         </is>
       </c>
-      <c r="B355" s="4" t="inlineStr">
+      <c r="B355" s="2" t="inlineStr">
         <is>
           <t>AEZ74533318</t>
         </is>
       </c>
-      <c r="C355" s="4" t="inlineStr"/>
-      <c r="D355" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E355" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C355" s="2" t="inlineStr">
+        <is>
+          <t>LG Range Control Knob Assembly, Stainless - AEZ74533318</t>
+        </is>
+      </c>
+      <c r="D355" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E355" s="2" t="inlineStr">
+        <is>
+          <t>Several sellers; models LSD4913ST/LSE4616ST</t>
         </is>
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="4" t="inlineStr">
+      <c r="A356" s="2" t="inlineStr">
         <is>
           <t>Liebherr</t>
         </is>
       </c>
-      <c r="B356" s="4" t="inlineStr">
+      <c r="B356" s="2" t="inlineStr">
         <is>
           <t>951793400</t>
         </is>
       </c>
-      <c r="C356" s="4" t="inlineStr"/>
-      <c r="D356" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E356" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>Liebherr Refrigerator Magnetic Door Strip - 951793400</t>
+        </is>
+      </c>
+      <c r="D356" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E356" s="2" t="inlineStr">
+        <is>
+          <t>Two Encompass model pages; one lists it also as an ice maker motor</t>
         </is>
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="4" t="inlineStr">
+      <c r="A357" s="3" t="inlineStr">
         <is>
           <t>Magic Chef</t>
         </is>
       </c>
-      <c r="B357" s="4" t="inlineStr">
+      <c r="B357" s="3" t="inlineStr">
         <is>
           <t>12138000039023</t>
         </is>
       </c>
-      <c r="C357" s="4" t="inlineStr"/>
-      <c r="D357" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E357" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C357" s="3" t="inlineStr"/>
+      <c r="D357" s="3" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
+      <c r="E357" s="3" t="inlineStr">
+        <is>
+          <t>Searched "12138000039023" Magic Chef; only a similar number (12138000039034) found</t>
         </is>
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="4" t="inlineStr">
+      <c r="A358" t="inlineStr">
         <is>
           <t>Magic Chef</t>
         </is>
       </c>
-      <c r="B358" s="4" t="inlineStr">
+      <c r="B358" t="inlineStr">
         <is>
           <t>1858900900</t>
         </is>
       </c>
-      <c r="C358" s="4" t="inlineStr"/>
-      <c r="D358" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E358" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Magic Chef Ice Maker Water Recirculation Pump - 1858900900</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>EWCIM44/65/90/120; several sellers</t>
         </is>
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="4" t="inlineStr">
+      <c r="A359" t="inlineStr">
         <is>
           <t>Magic Chef</t>
         </is>
       </c>
-      <c r="B359" s="4" t="inlineStr">
+      <c r="B359" t="inlineStr">
         <is>
           <t>30108000003</t>
         </is>
       </c>
-      <c r="C359" s="4" t="inlineStr"/>
-      <c r="D359" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E359" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Magic Chef Range Hot Surface Igniter - 30108000003</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>MCSRG24S/MCSBRG24B; several sellers</t>
         </is>
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="4" t="inlineStr">
+      <c r="A360" t="inlineStr">
         <is>
           <t>Magic Chef</t>
         </is>
       </c>
-      <c r="B360" s="4" t="inlineStr">
+      <c r="B360" t="inlineStr">
         <is>
           <t>30401800022</t>
         </is>
       </c>
-      <c r="C360" s="4" t="inlineStr"/>
-      <c r="D360" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E360" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Magic Chef Range Surface Burner Thermocouple, Left Front Triple Ring - 30401800022</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>MCSCTG24S/MCSRG24S; Parts Town and MC Appliance</t>
         </is>
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="4" t="inlineStr">
+      <c r="A361" t="inlineStr">
         <is>
           <t>Magic Chef</t>
         </is>
       </c>
-      <c r="B361" s="4" t="inlineStr">
+      <c r="B361" t="inlineStr">
         <is>
           <t>312180200324</t>
         </is>
       </c>
-      <c r="C361" s="4" t="inlineStr"/>
-      <c r="D361" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E361" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Magic Chef Wine Cooler Display PCB - 312180200324</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>HMWC50/HMBC58 coolers; several sellers</t>
         </is>
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="4" t="inlineStr">
+      <c r="A362" s="2" t="inlineStr">
         <is>
           <t>Magic Chef</t>
         </is>
       </c>
-      <c r="B362" s="4" t="inlineStr">
+      <c r="B362" s="2" t="inlineStr">
         <is>
           <t>312260100011</t>
         </is>
       </c>
-      <c r="C362" s="4" t="inlineStr"/>
-      <c r="D362" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E362" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>Magic Chef Wine Cooler Door Assembly - 312260100011</t>
+        </is>
+      </c>
+      <c r="D362" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E362" s="2" t="inlineStr">
+        <is>
+          <t>Single Parts Town listing for MCWBC77DZC</t>
         </is>
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="4" t="inlineStr">
+      <c r="A363" s="3" t="inlineStr">
         <is>
           <t>Magic Chef</t>
         </is>
       </c>
-      <c r="B363" s="4" t="inlineStr">
+      <c r="B363" s="3" t="inlineStr">
         <is>
           <t>64836</t>
         </is>
       </c>
-      <c r="C363" s="4" t="inlineStr"/>
-      <c r="D363" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E363" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C363" s="3" t="inlineStr">
+        <is>
+          <t>Magic Chef Splice Box, Starter, Overload Protector &amp; Start Capacitor Set - 64836</t>
+        </is>
+      </c>
+      <c r="D363" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E363" s="3" t="inlineStr">
+        <is>
+          <t>Single MC Appliance listing; equipment type not stated (refrigeration relay set)</t>
         </is>
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="4" t="inlineStr">
+      <c r="A364" s="3" t="inlineStr">
         <is>
           <t>Magic Chef</t>
         </is>
       </c>
-      <c r="B364" s="4" t="inlineStr">
+      <c r="B364" s="3" t="inlineStr">
         <is>
           <t>76839</t>
         </is>
       </c>
-      <c r="C364" s="4" t="inlineStr"/>
-      <c r="D364" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E364" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C364" s="3" t="inlineStr"/>
+      <c r="D364" s="3" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
+      <c r="E364" s="3" t="inlineStr">
+        <is>
+          <t>Searched "76839" Magic Chef; no listing found</t>
         </is>
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="4" t="inlineStr">
+      <c r="A365" s="2" t="inlineStr">
         <is>
           <t>Magic Chef</t>
         </is>
       </c>
-      <c r="B365" s="4" t="inlineStr">
+      <c r="B365" s="2" t="inlineStr">
         <is>
           <t>D155TDOP02.01</t>
         </is>
       </c>
-      <c r="C365" s="4" t="inlineStr"/>
-      <c r="D365" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E365" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C365" s="2" t="inlineStr">
+        <is>
+          <t>Magic Chef Wine Cooler Temperature Control PCB - D155TDOP02.01</t>
+        </is>
+      </c>
+      <c r="D365" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E365" s="2" t="inlineStr">
+        <is>
+          <t>Parts Town and MC Appliance; "44DZ Huada" board, appliance model not confirmed</t>
         </is>
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="4" t="inlineStr">
+      <c r="A366" s="3" t="inlineStr">
         <is>
           <t>Marshall Air</t>
         </is>
       </c>
-      <c r="B366" s="4" t="inlineStr">
+      <c r="B366" s="3" t="inlineStr">
         <is>
           <t>148000</t>
         </is>
       </c>
-      <c r="C366" s="4" t="inlineStr"/>
-      <c r="D366" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E366" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C366" s="3" t="inlineStr">
+        <is>
+          <t>Marshall Air Lower Heating Element 350W - 148000</t>
+        </is>
+      </c>
+      <c r="D366" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E366" s="3" t="inlineStr">
+        <is>
+          <t>Parts Town only; BW4B-3/DL2 fit, equipment type not stated</t>
         </is>
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="4" t="inlineStr">
+      <c r="A367" s="3" t="inlineStr">
         <is>
           <t>Marshall Air</t>
         </is>
       </c>
-      <c r="B367" s="4" t="inlineStr">
+      <c r="B367" s="3" t="inlineStr">
         <is>
           <t>504023</t>
         </is>
       </c>
-      <c r="C367" s="4" t="inlineStr"/>
-      <c r="D367" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E367" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C367" s="3" t="inlineStr">
+        <is>
+          <t>Marshall Air Solid State Relay 240VAC 25A - 504023</t>
+        </is>
+      </c>
+      <c r="D367" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E367" s="3" t="inlineStr">
+        <is>
+          <t>Several sellers; fits HST13, equipment type not stated</t>
         </is>
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="4" t="inlineStr">
+      <c r="A368" s="2" t="inlineStr">
         <is>
           <t>Marshall Air</t>
         </is>
       </c>
-      <c r="B368" s="4" t="inlineStr">
+      <c r="B368" s="2" t="inlineStr">
         <is>
           <t>504140</t>
         </is>
       </c>
-      <c r="C368" s="4" t="inlineStr"/>
-      <c r="D368" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E368" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>Marshall Air Food Warmer Appliance Lamp 40W 130V - 504140</t>
+        </is>
+      </c>
+      <c r="D368" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E368" s="2" t="inlineStr">
+        <is>
+          <t>Fits warmer KK6; some Amazon listings say 60W</t>
         </is>
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="4" t="inlineStr">
+      <c r="A369" s="2" t="inlineStr">
         <is>
           <t>Midea</t>
         </is>
       </c>
-      <c r="B369" s="4" t="inlineStr">
+      <c r="B369" s="2" t="inlineStr">
         <is>
           <t>12231000044469</t>
         </is>
       </c>
-      <c r="C369" s="4" t="inlineStr"/>
-      <c r="D369" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E369" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C369" s="2" t="inlineStr">
+        <is>
+          <t>Midea Refrigerator Door Stopper - 12231000044469</t>
+        </is>
+      </c>
+      <c r="D369" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E369" s="2" t="inlineStr">
+        <is>
+          <t>Several Encompass model pages and eBay</t>
         </is>
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="4" t="inlineStr">
+      <c r="A370" s="2" t="inlineStr">
         <is>
           <t>Midea</t>
         </is>
       </c>
-      <c r="B370" s="4" t="inlineStr">
+      <c r="B370" s="2" t="inlineStr">
         <is>
           <t>16376000000262</t>
         </is>
       </c>
-      <c r="C370" s="4" t="inlineStr"/>
-      <c r="D370" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E370" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>Midea Dishwasher Accessory Bag - 16376000000262</t>
+        </is>
+      </c>
+      <c r="D370" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E370" s="2" t="inlineStr">
+        <is>
+          <t>iFixit and Parts Town; discontinued</t>
         </is>
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="4" t="inlineStr">
+      <c r="A371" s="2" t="inlineStr">
         <is>
           <t>Midea</t>
         </is>
       </c>
-      <c r="B371" s="4" t="inlineStr">
+      <c r="B371" s="2" t="inlineStr">
         <is>
           <t>17438000023702</t>
         </is>
       </c>
-      <c r="C371" s="4" t="inlineStr"/>
-      <c r="D371" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E371" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C371" s="2" t="inlineStr">
+        <is>
+          <t>Midea Washer Water Level Sensor - 17438000023702</t>
+        </is>
+      </c>
+      <c r="D371" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E371" s="2" t="inlineStr">
+        <is>
+          <t>Midea washer-dryer models; one Encompass page labels it Insignia</t>
         </is>
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="4" t="inlineStr">
+      <c r="A372" s="2" t="inlineStr">
         <is>
           <t>Midea</t>
         </is>
       </c>
-      <c r="B372" s="4" t="inlineStr">
+      <c r="B372" s="2" t="inlineStr">
         <is>
           <t>17471100004767</t>
         </is>
       </c>
-      <c r="C372" s="4" t="inlineStr"/>
-      <c r="D372" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E372" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>Midea Range Cooktop Hot Surface Indicator Light - 17471100004767</t>
+        </is>
+      </c>
+      <c r="D372" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E372" s="2" t="inlineStr">
+        <is>
+          <t>MES30S2AST slide-in range; three parts-lookup pages</t>
         </is>
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="4" t="inlineStr">
+      <c r="A373" s="2" t="inlineStr">
         <is>
           <t>Midea</t>
         </is>
       </c>
-      <c r="B373" s="4" t="inlineStr">
+      <c r="B373" s="2" t="inlineStr">
         <is>
           <t>17476000A05315</t>
         </is>
       </c>
-      <c r="C373" s="4" t="inlineStr"/>
-      <c r="D373" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E373" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>Midea Dishwasher Pumpcase / Wash Pump Assembly - 17476000A05315</t>
+        </is>
+      </c>
+      <c r="D373" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E373" s="2" t="inlineStr">
+        <is>
+          <t>Retailers say pumpcase, iFixit says wash pump with heater</t>
         </is>
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="4" t="inlineStr">
+      <c r="A374" s="2" t="inlineStr">
         <is>
           <t>Mitsubishi</t>
         </is>
       </c>
-      <c r="B374" s="4" t="inlineStr">
+      <c r="B374" s="2" t="inlineStr">
         <is>
           <t>E22A49340</t>
         </is>
       </c>
-      <c r="C374" s="4" t="inlineStr"/>
-      <c r="D374" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E374" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>Mitsubishi Mini Split Contactor / Relay 120V - E22A49340</t>
+        </is>
+      </c>
+      <c r="D374" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E374" s="2" t="inlineStr">
+        <is>
+          <t>Sellers disagree on SPST relay vs contactor; ductless mini-split per one seller</t>
         </is>
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="4" t="inlineStr">
+      <c r="A375" t="inlineStr">
         <is>
           <t>Moffat</t>
         </is>
       </c>
-      <c r="B375" s="4" t="inlineStr">
+      <c r="B375" t="inlineStr">
         <is>
           <t>025997K</t>
         </is>
       </c>
-      <c r="C375" s="4" t="inlineStr"/>
-      <c r="D375" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E375" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Moffat Holding Cabinet Air Temperature Probe Kit (HP10T) - 025997K</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Moffat HP10T parts manual and sellers</t>
         </is>
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="4" t="inlineStr">
+      <c r="A376" s="2" t="inlineStr">
         <is>
           <t>Moffat</t>
         </is>
       </c>
-      <c r="B376" s="4" t="inlineStr">
+      <c r="B376" s="2" t="inlineStr">
         <is>
           <t>241895</t>
         </is>
       </c>
-      <c r="C376" s="4" t="inlineStr"/>
-      <c r="D376" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E376" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C376" s="2" t="inlineStr">
+        <is>
+          <t>Moffat Holding Cabinet Lamp Holder G9 25W - 241895</t>
+        </is>
+      </c>
+      <c r="D376" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E376" s="2" t="inlineStr">
+        <is>
+          <t>Single source: Moffat HP10T service manual</t>
         </is>
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="4" t="inlineStr">
+      <c r="A377" t="inlineStr">
         <is>
           <t>Moffat</t>
         </is>
       </c>
-      <c r="B377" s="4" t="inlineStr">
+      <c r="B377" t="inlineStr">
         <is>
           <t>M020083</t>
         </is>
       </c>
-      <c r="C377" s="4" t="inlineStr"/>
-      <c r="D377" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E377" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Moffat Convection Oven Bottom Hinge Assembly (E32/E89M) - M020083</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Many sellers agree</t>
         </is>
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="4" t="inlineStr">
+      <c r="A378" t="inlineStr">
         <is>
           <t>Moffat</t>
         </is>
       </c>
-      <c r="B378" s="4" t="inlineStr">
+      <c r="B378" t="inlineStr">
         <is>
           <t>M231438</t>
         </is>
       </c>
-      <c r="C378" s="4" t="inlineStr"/>
-      <c r="D378" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E378" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Moffat Convection Oven Door Seal Gasket (E35) - M231438</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Many sellers agree; dimensions vary</t>
         </is>
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="4" t="inlineStr">
+      <c r="A379" t="inlineStr">
         <is>
           <t>Moffat</t>
         </is>
       </c>
-      <c r="B379" s="4" t="inlineStr">
+      <c r="B379" t="inlineStr">
         <is>
           <t>M234757</t>
         </is>
       </c>
-      <c r="C379" s="4" t="inlineStr"/>
-      <c r="D379" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E379" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Moffat Convection Oven Inner Door Glass Assembly (E32D/G32D) - M234757</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Many sellers agree</t>
         </is>
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="4" t="inlineStr">
+      <c r="A380" t="inlineStr">
         <is>
           <t>Moffat</t>
         </is>
       </c>
-      <c r="B380" s="4" t="inlineStr">
+      <c r="B380" t="inlineStr">
         <is>
           <t>M237548</t>
         </is>
       </c>
-      <c r="C380" s="4" t="inlineStr"/>
-      <c r="D380" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E380" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Moffat Convection Oven Fan Motor Kit (E32D5) - M237548</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Sellers call it fan motor or motor kit</t>
         </is>
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="4" t="inlineStr">
+      <c r="A381" s="3" t="inlineStr">
         <is>
           <t>Napoleon</t>
         </is>
       </c>
-      <c r="B381" s="4" t="inlineStr">
+      <c r="B381" s="3" t="inlineStr">
         <is>
           <t>1854005700</t>
         </is>
       </c>
-      <c r="C381" s="4" t="inlineStr"/>
-      <c r="D381" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E381" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C381" s="3" t="inlineStr"/>
+      <c r="D381" s="3" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
+      <c r="E381" s="3" t="inlineStr">
+        <is>
+          <t>Number is listed as a Magic Chef/Norpole/Maxx Ice ice maker sensor; no Napoleon listing found, brand conflict</t>
         </is>
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="4" t="inlineStr">
+      <c r="A382" t="inlineStr">
         <is>
           <t>Nu-Vu</t>
         </is>
       </c>
-      <c r="B382" s="4" t="inlineStr">
+      <c r="B382" t="inlineStr">
         <is>
           <t>252-4001</t>
         </is>
       </c>
-      <c r="C382" s="4" t="inlineStr"/>
-      <c r="D382" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E382" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Nu-Vu Proofer Solid State Thermostat 250°F - 252-4001</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Fits OP-2FM; many sellers; also listed as Star Mfg</t>
         </is>
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="4" t="inlineStr">
+      <c r="A383" s="2" t="inlineStr">
         <is>
           <t>Nu-Vu</t>
         </is>
       </c>
-      <c r="B383" s="4" t="inlineStr">
+      <c r="B383" s="2" t="inlineStr">
         <is>
           <t>253-2003</t>
         </is>
       </c>
-      <c r="C383" s="4" t="inlineStr"/>
-      <c r="D383" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E383" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C383" s="2" t="inlineStr">
+        <is>
+          <t>Nu-Vu Oven Temperature Control Knob - 253-2003</t>
+        </is>
+      </c>
+      <c r="D383" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E383" s="2" t="inlineStr">
+        <is>
+          <t>Fits OP-2FM, PROW-18, SUB-123; type inferred</t>
         </is>
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="4" t="inlineStr">
+      <c r="A384" s="2" t="inlineStr">
         <is>
           <t>Nu-Vu</t>
         </is>
       </c>
-      <c r="B384" s="4" t="inlineStr">
+      <c r="B384" s="2" t="inlineStr">
         <is>
           <t>66-5048</t>
         </is>
       </c>
-      <c r="C384" s="4" t="inlineStr"/>
-      <c r="D384" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E384" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C384" s="2" t="inlineStr">
+        <is>
+          <t>Nu-Vu Oven Low Profile Motor 1/2 HP 3PH 230V - 66-5048</t>
+        </is>
+      </c>
+      <c r="D384" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E384" s="2" t="inlineStr">
+        <is>
+          <t>Sellers split Nu-Vu vs Star Mfg branding</t>
         </is>
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="4" t="inlineStr">
+      <c r="A385" s="2" t="inlineStr">
         <is>
           <t>Nu-Vu</t>
         </is>
       </c>
-      <c r="B385" s="4" t="inlineStr">
+      <c r="B385" s="2" t="inlineStr">
         <is>
           <t>98-9911</t>
         </is>
       </c>
-      <c r="C385" s="4" t="inlineStr"/>
-      <c r="D385" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E385" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C385" s="2" t="inlineStr">
+        <is>
+          <t>Nu-Vu Oven Left-Hinged Glass Door Assembly (XO-1) - 98-9911</t>
+        </is>
+      </c>
+      <c r="D385" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E385" s="2" t="inlineStr">
+        <is>
+          <t>Two seller listings</t>
         </is>
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="4" t="inlineStr">
+      <c r="A386" s="3" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="B386" s="4" t="inlineStr">
+      <c r="B386" s="3" t="inlineStr">
         <is>
           <t>DG94-02841A</t>
         </is>
       </c>
-      <c r="C386" s="4" t="inlineStr"/>
-      <c r="D386" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E386" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C386" s="3" t="inlineStr"/>
+      <c r="D386" s="3" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
+      <c r="E386" s="3" t="inlineStr">
+        <is>
+          <t>Searched "DG94-02841A" Samsung; no listing found, only neighbouring DG94 numbers</t>
         </is>
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="4" t="inlineStr">
+      <c r="A387" s="2" t="inlineStr">
         <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="B387" s="4" t="inlineStr">
+      <c r="B387" s="2" t="inlineStr">
         <is>
           <t>DC92-00669Y</t>
         </is>
       </c>
-      <c r="C387" s="4" t="inlineStr"/>
-      <c r="D387" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E387" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C387" s="2" t="inlineStr">
+        <is>
+          <t>Samsung Dryer Main Control Board Assembly - DC92-00669Y</t>
+        </is>
+      </c>
+      <c r="D387" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E387" s="2" t="inlineStr">
+        <is>
+          <t>Most sellers say dryer board/holder; one Amazon listing says dishwasher</t>
         </is>
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="4" t="inlineStr">
+      <c r="A388" t="inlineStr">
         <is>
           <t>Scotsman</t>
         </is>
       </c>
-      <c r="B388" s="4" t="inlineStr">
+      <c r="B388" t="inlineStr">
         <is>
           <t>11-0531-21</t>
         </is>
       </c>
-      <c r="C388" s="4" t="inlineStr"/>
-      <c r="D388" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E388" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Scotsman Ice Machine Purge Valve Timer - 11-0531-21</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Scotsman price list and sellers; CME ice machines</t>
         </is>
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="4" t="inlineStr">
+      <c r="A389" t="inlineStr">
         <is>
           <t>Scotsman</t>
         </is>
       </c>
-      <c r="B389" s="4" t="inlineStr">
+      <c r="B389" t="inlineStr">
         <is>
           <t>16-1122-21</t>
         </is>
       </c>
-      <c r="C389" s="4" t="inlineStr"/>
-      <c r="D389" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E389" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Scotsman Ice Machine Accumulator Kit with Insulation - 16-1122-21</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Scotsman MC2648 service parts and sellers</t>
         </is>
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="4" t="inlineStr">
+      <c r="A390" t="inlineStr">
         <is>
           <t>Scotsman</t>
         </is>
       </c>
-      <c r="B390" s="4" t="inlineStr">
+      <c r="B390" t="inlineStr">
         <is>
           <t>16-1140-01</t>
         </is>
       </c>
-      <c r="C390" s="4" t="inlineStr"/>
-      <c r="D390" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E390" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Scotsman Ice Machine Access Valve Service Port Cap - 16-1140-01</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Scotsman service parts lists</t>
         </is>
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="4" t="inlineStr">
+      <c r="A391" t="inlineStr">
         <is>
           <t>Scotsman</t>
         </is>
       </c>
-      <c r="B391" s="4" t="inlineStr">
+      <c r="B391" t="inlineStr">
         <is>
           <t>16-1182-01</t>
         </is>
       </c>
-      <c r="C391" s="4" t="inlineStr"/>
-      <c r="D391" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E391" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Scotsman Ice Machine Thermostatic Expansion Valve (TUC) - 16-1182-01</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Scotsman MC0630 parts list and sellers</t>
         </is>
       </c>
     </row>

--- a/Book_H1_tags.xlsx
+++ b/Book_H1_tags.xlsx
@@ -29,7 +29,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -46,11 +46,6 @@
         <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -64,12 +59,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -10899,646 +10893,750 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="4" t="inlineStr">
+      <c r="A392" t="inlineStr">
         <is>
           <t>Scotsman</t>
         </is>
       </c>
-      <c r="B392" s="4" t="inlineStr">
+      <c r="B392" t="inlineStr">
         <is>
           <t>R620314803</t>
         </is>
       </c>
-      <c r="C392" s="4" t="inlineStr"/>
-      <c r="D392" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E392" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Scotsman Ice Machine Agitation Timer 120V - R620314803</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Amazon, Parts Town and FixIce (ID150/ID200 dispensers)</t>
         </is>
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="4" t="inlineStr">
+      <c r="A393" t="inlineStr">
         <is>
           <t>Sharp</t>
         </is>
       </c>
-      <c r="B393" s="4" t="inlineStr">
+      <c r="B393" t="inlineStr">
         <is>
           <t>FGLSPA069WRFZ</t>
         </is>
       </c>
-      <c r="C393" s="4" t="inlineStr"/>
-      <c r="D393" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E393" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Sharp Microwave Oven Oven Tray Assembly - FGLSPA069WRFZ</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Sharp commercial microwaves RCD1800M/RCD2200M; several sellers</t>
         </is>
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="4" t="inlineStr">
+      <c r="A394" s="2" t="inlineStr">
         <is>
           <t>Sony</t>
         </is>
       </c>
-      <c r="B394" s="4" t="inlineStr">
+      <c r="B394" s="2" t="inlineStr">
         <is>
           <t>A-5014-378-A</t>
         </is>
       </c>
-      <c r="C394" s="4" t="inlineStr"/>
-      <c r="D394" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E394" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C394" s="2" t="inlineStr">
+        <is>
+          <t>Sony TV ONT J Board - A-5014-378-A</t>
+        </is>
+      </c>
+      <c r="D394" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E394" s="2" t="inlineStr">
+        <is>
+          <t>Sellers disagree on name (ONT J board vs Compl Svc ONTJ_NE); XBR-75/85Z8H</t>
         </is>
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="4" t="inlineStr">
+      <c r="A395" s="3" t="inlineStr">
         <is>
           <t>Sony</t>
         </is>
       </c>
-      <c r="B395" s="4" t="inlineStr">
+      <c r="B395" s="3" t="inlineStr">
         <is>
           <t>A-5057-109-A</t>
         </is>
       </c>
-      <c r="C395" s="4" t="inlineStr"/>
-      <c r="D395" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E395" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C395" s="3" t="inlineStr"/>
+      <c r="D395" s="3" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
+      <c r="E395" s="3" t="inlineStr">
+        <is>
+          <t>Searched "A-5057-109-A" Sony; no listing found, only neighbouring A-5057 numbers</t>
         </is>
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="4" t="inlineStr">
+      <c r="A396" s="2" t="inlineStr">
         <is>
           <t>Speed Queen</t>
         </is>
       </c>
-      <c r="B396" s="4" t="inlineStr">
+      <c r="B396" s="2" t="inlineStr">
         <is>
           <t>70482901</t>
         </is>
       </c>
-      <c r="C396" s="4" t="inlineStr"/>
-      <c r="D396" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E396" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>Speed Queen Washer Door Catch Kit - 70482901</t>
+        </is>
+      </c>
+      <c r="D396" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E396" s="2" t="inlineStr">
+        <is>
+          <t>Alliance Laundry store lists it for washers and dryers</t>
         </is>
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="4" t="inlineStr">
+      <c r="A397" t="inlineStr">
         <is>
           <t>Turbochef</t>
         </is>
       </c>
-      <c r="B397" s="4" t="inlineStr">
+      <c r="B397" t="inlineStr">
         <is>
           <t>103566</t>
         </is>
       </c>
-      <c r="C397" s="4" t="inlineStr"/>
-      <c r="D397" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E397" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Turbochef Oven Fuse Block 3-Pole 600V 30A - 103566</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Parts Town and Encore service manual</t>
         </is>
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="4" t="inlineStr">
+      <c r="A398" s="2" t="inlineStr">
         <is>
           <t>Turbochef</t>
         </is>
       </c>
-      <c r="B398" s="4" t="inlineStr">
+      <c r="B398" s="2" t="inlineStr">
         <is>
           <t>301365</t>
         </is>
       </c>
-      <c r="C398" s="4" t="inlineStr"/>
-      <c r="D398" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E398" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C398" s="2" t="inlineStr">
+        <is>
+          <t>Turbochef Oven Temperature Sensor Assembly - 301365</t>
+        </is>
+      </c>
+      <c r="D398" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E398" s="2" t="inlineStr">
+        <is>
+          <t>Single Parts Town listing; discontinued</t>
         </is>
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="4" t="inlineStr">
+      <c r="A399" s="3" t="inlineStr">
         <is>
           <t>Turbochef</t>
         </is>
       </c>
-      <c r="B399" s="4" t="inlineStr">
+      <c r="B399" s="3" t="inlineStr">
         <is>
           <t>301684</t>
         </is>
       </c>
-      <c r="C399" s="4" t="inlineStr"/>
-      <c r="D399" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E399" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C399" s="3" t="inlineStr">
+        <is>
+          <t>Turbochef Oven Power Output Stage Assembly, 3 Phase - 301684</t>
+        </is>
+      </c>
+      <c r="D399" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E399" s="3" t="inlineStr">
+        <is>
+          <t>Single old catalog page; price/details unconfirmed</t>
         </is>
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="4" t="inlineStr">
+      <c r="A400" t="inlineStr">
         <is>
           <t>Turbochef</t>
         </is>
       </c>
-      <c r="B400" s="4" t="inlineStr">
+      <c r="B400" t="inlineStr">
         <is>
           <t>CON-3046</t>
         </is>
       </c>
-      <c r="C400" s="4" t="inlineStr"/>
-      <c r="D400" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E400" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Turbochef Oven Control Board Service Kit - CON-3046</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Many sellers; HHD / Sage T models</t>
         </is>
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="4" t="inlineStr">
+      <c r="A401" s="2" t="inlineStr">
         <is>
           <t>Turbochef</t>
         </is>
       </c>
-      <c r="B401" s="4" t="inlineStr">
+      <c r="B401" s="2" t="inlineStr">
         <is>
           <t>ECO-3212</t>
         </is>
       </c>
-      <c r="C401" s="4" t="inlineStr"/>
-      <c r="D401" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E401" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C401" s="2" t="inlineStr">
+        <is>
+          <t>Turbochef Oven Service Kit, Phoenix to HLUI (ECO) - ECO-3212</t>
+        </is>
+      </c>
+      <c r="D401" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E401" s="2" t="inlineStr">
+        <is>
+          <t>Single Turbochef Canada listing; I1-3212 stirrer is a different part</t>
         </is>
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="4" t="inlineStr">
+      <c r="A402" t="inlineStr">
         <is>
           <t>Turbochef</t>
         </is>
       </c>
-      <c r="B402" s="4" t="inlineStr">
+      <c r="B402" t="inlineStr">
         <is>
           <t>ENC-3005-1</t>
         </is>
       </c>
-      <c r="C402" s="4" t="inlineStr"/>
-      <c r="D402" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E402" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Turbochef Oven Encore Light Ring Service Kit - ENC-3005-1</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Fits Encore / Encore 2; many sellers</t>
         </is>
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="4" t="inlineStr">
+      <c r="A403" s="2" t="inlineStr">
         <is>
           <t>Turbochef</t>
         </is>
       </c>
-      <c r="B403" s="4" t="inlineStr">
+      <c r="B403" s="2" t="inlineStr">
         <is>
           <t>ENC-3010-1</t>
         </is>
       </c>
-      <c r="C403" s="4" t="inlineStr"/>
-      <c r="D403" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E403" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C403" s="2" t="inlineStr">
+        <is>
+          <t>Turbochef Oven Capacitor 2500V 50/60Hz - ENC-3010-1</t>
+        </is>
+      </c>
+      <c r="D403" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E403" s="2" t="inlineStr">
+        <is>
+          <t>Parts Town, Webstaurant and eBay; no model list</t>
         </is>
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="4" t="inlineStr">
+      <c r="A404" t="inlineStr">
         <is>
           <t>Turbochef</t>
         </is>
       </c>
-      <c r="B404" s="4" t="inlineStr">
+      <c r="B404" t="inlineStr">
         <is>
           <t>ENC-3011</t>
         </is>
       </c>
-      <c r="C404" s="4" t="inlineStr"/>
-      <c r="D404" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E404" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Turbochef Oven 4.3" TFT Display Board Service Kit - ENC-3011</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Encore / Encore 2 / NGO; many sellers</t>
         </is>
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="4" t="inlineStr">
+      <c r="A405" t="inlineStr">
         <is>
           <t>Turbochef</t>
         </is>
       </c>
-      <c r="B405" s="4" t="inlineStr">
+      <c r="B405" t="inlineStr">
         <is>
           <t>ENC-3022</t>
         </is>
       </c>
-      <c r="C405" s="4" t="inlineStr"/>
-      <c r="D405" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E405" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Turbochef Oven Door Hinge Kit with Springs (Set of 2) - ENC-3022</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Many sellers agree</t>
         </is>
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="4" t="inlineStr">
+      <c r="A406" s="3" t="inlineStr">
         <is>
           <t>Turbochef</t>
         </is>
       </c>
-      <c r="B406" s="4" t="inlineStr">
+      <c r="B406" s="3" t="inlineStr">
         <is>
           <t>HCT-4401</t>
         </is>
       </c>
-      <c r="C406" s="4" t="inlineStr"/>
-      <c r="D406" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E406" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C406" s="3" t="inlineStr">
+        <is>
+          <t>Turbochef Oven Low Voltage Harness - HCT-4401</t>
+        </is>
+      </c>
+      <c r="D406" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E406" s="3" t="inlineStr">
+        <is>
+          <t>Two listings only, no price or fit information</t>
         </is>
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="4" t="inlineStr">
+      <c r="A407" t="inlineStr">
         <is>
           <t>Turbochef</t>
         </is>
       </c>
-      <c r="B407" s="4" t="inlineStr">
+      <c r="B407" t="inlineStr">
         <is>
           <t>HHB-3204</t>
         </is>
       </c>
-      <c r="C407" s="4" t="inlineStr"/>
-      <c r="D407" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E407" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Turbochef Oven Display Service Kit (HHB) - HHB-3204</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Many sellers agree</t>
         </is>
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="4" t="inlineStr">
+      <c r="A408" t="inlineStr">
         <is>
           <t>Turbochef</t>
         </is>
       </c>
-      <c r="B408" s="4" t="inlineStr">
+      <c r="B408" t="inlineStr">
         <is>
           <t>HHC-4120</t>
         </is>
       </c>
-      <c r="C408" s="4" t="inlineStr"/>
-      <c r="D408" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E408" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Turbochef Conveyor Oven Conveyor Gear Motor 1/50 HP 208/230V - HHC-4120</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>HHC series; several sellers</t>
         </is>
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="4" t="inlineStr">
+      <c r="A409" t="inlineStr">
         <is>
           <t>Turbochef</t>
         </is>
       </c>
-      <c r="B409" s="4" t="inlineStr">
+      <c r="B409" t="inlineStr">
         <is>
           <t>HHD-3003</t>
         </is>
       </c>
-      <c r="C409" s="4" t="inlineStr"/>
-      <c r="D409" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E409" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Turbochef Oven Heater Assembly Service Kit (HHD) - HHD-3003</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>HHD double batch ovens; many sellers</t>
         </is>
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="4" t="inlineStr">
+      <c r="A410" s="2" t="inlineStr">
         <is>
           <t>Turbochef</t>
         </is>
       </c>
-      <c r="B410" s="4" t="inlineStr">
+      <c r="B410" s="2" t="inlineStr">
         <is>
           <t>I1-3201-10</t>
         </is>
       </c>
-      <c r="C410" s="4" t="inlineStr"/>
-      <c r="D410" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E410" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C410" s="2" t="inlineStr">
+        <is>
+          <t>Turbochef Oven Oven Door, Black - I1-3201-10</t>
+        </is>
+      </c>
+      <c r="D410" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E410" s="2" t="inlineStr">
+        <is>
+          <t>AllPoints and Turbochef Canada; two sellers</t>
         </is>
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="4" t="inlineStr">
+      <c r="A411" t="inlineStr">
         <is>
           <t>Turbochef</t>
         </is>
       </c>
-      <c r="B411" s="4" t="inlineStr">
+      <c r="B411" t="inlineStr">
         <is>
           <t>I1-9166</t>
         </is>
       </c>
-      <c r="C411" s="4" t="inlineStr"/>
-      <c r="D411" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E411" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Turbochef Oven Cooking Basket, Solid PTFE 11.5" x 8.5" - I1-9166</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>Several sellers; obsolete, replaced by 105696</t>
         </is>
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="4" t="inlineStr">
+      <c r="A412" t="inlineStr">
         <is>
           <t>Turbochef</t>
         </is>
       </c>
-      <c r="B412" s="4" t="inlineStr">
+      <c r="B412" t="inlineStr">
         <is>
           <t>I3-3231</t>
         </is>
       </c>
-      <c r="C412" s="4" t="inlineStr"/>
-      <c r="D412" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E412" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Turbochef Oven Touchscreen Service Kit, Phoenix to HLUI (i3) - I3-3231</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Many sellers agree</t>
         </is>
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="4" t="inlineStr">
+      <c r="A413" s="2" t="inlineStr">
         <is>
           <t>Turbochef</t>
         </is>
       </c>
-      <c r="B413" s="4" t="inlineStr">
+      <c r="B413" s="2" t="inlineStr">
         <is>
           <t>I5-9378</t>
         </is>
       </c>
-      <c r="C413" s="4" t="inlineStr"/>
-      <c r="D413" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E413" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C413" s="2" t="inlineStr">
+        <is>
+          <t>Turbochef Oven Capacitor Jumper Wire - I5-9378</t>
+        </is>
+      </c>
+      <c r="D413" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E413" s="2" t="inlineStr">
+        <is>
+          <t>Parts Town and Middleby Advantage; one result is a different part (I3-9378 heater)</t>
         </is>
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="4" t="inlineStr">
+      <c r="A414" t="inlineStr">
         <is>
           <t>Turbochef</t>
         </is>
       </c>
-      <c r="B414" s="4" t="inlineStr">
+      <c r="B414" t="inlineStr">
         <is>
           <t>NGC-3005</t>
         </is>
       </c>
-      <c r="C414" s="4" t="inlineStr"/>
-      <c r="D414" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E414" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Turbochef Oven Dual 40A Solid State Relay 120/240V - NGC-3005</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Many sellers; NGC/HHB/i3 ovens</t>
         </is>
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="4" t="inlineStr">
+      <c r="A415" s="2" t="inlineStr">
         <is>
           <t>Turbochef</t>
         </is>
       </c>
-      <c r="B415" s="4" t="inlineStr">
+      <c r="B415" s="2" t="inlineStr">
         <is>
           <t>PLE-3228</t>
         </is>
       </c>
-      <c r="C415" s="4" t="inlineStr"/>
-      <c r="D415" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E415" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C415" s="2" t="inlineStr">
+        <is>
+          <t>Turbochef Oven Switch Service Kit (Plexor) - PLE-3228</t>
+        </is>
+      </c>
+      <c r="D415" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E415" s="2" t="inlineStr">
+        <is>
+          <t>Parts Town Plexor A3 pages; description is generic</t>
         </is>
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="4" t="inlineStr">
+      <c r="A416" t="inlineStr">
         <is>
           <t>U-Line</t>
         </is>
       </c>
-      <c r="B416" s="4" t="inlineStr">
+      <c r="B416" t="inlineStr">
         <is>
           <t>80-54138-00</t>
         </is>
       </c>
-      <c r="C416" s="4" t="inlineStr"/>
-      <c r="D416" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E416" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>U-Line Refrigerator Condenser Fan Motor - 80-54138-00</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Several sellers and model parts lists</t>
         </is>
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="4" t="inlineStr">
+      <c r="A417" s="2" t="inlineStr">
         <is>
           <t>U-Line</t>
         </is>
       </c>
-      <c r="B417" s="4" t="inlineStr">
+      <c r="B417" s="2" t="inlineStr">
         <is>
           <t>80-54149-00</t>
         </is>
       </c>
-      <c r="C417" s="4" t="inlineStr"/>
-      <c r="D417" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E417" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C417" s="2" t="inlineStr">
+        <is>
+          <t>U-Line Refrigerator Compressor Electrical Kit (Compressor Electricals Only) - 80-54149-00</t>
+        </is>
+      </c>
+      <c r="D417" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E417" s="2" t="inlineStr">
+        <is>
+          <t>U-Line parts documents; limited seller listings</t>
         </is>
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="4" t="inlineStr">
+      <c r="A418" s="3" t="inlineStr">
         <is>
           <t>Whirlpool</t>
         </is>
       </c>
-      <c r="B418" s="4" t="inlineStr">
+      <c r="B418" s="3" t="inlineStr">
         <is>
           <t>300248</t>
         </is>
       </c>
-      <c r="C418" s="4" t="inlineStr"/>
-      <c r="D418" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E418" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C418" s="3" t="inlineStr"/>
+      <c r="D418" s="3" t="inlineStr">
+        <is>
+          <t>Needs review</t>
+        </is>
+      </c>
+      <c r="E418" s="3" t="inlineStr">
+        <is>
+          <t>Searched "300248" Whirlpool; no matching listing found</t>
         </is>
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="4" t="inlineStr">
+      <c r="A419" t="inlineStr">
         <is>
           <t>York</t>
         </is>
       </c>
-      <c r="B419" s="4" t="inlineStr">
+      <c r="B419" t="inlineStr">
         <is>
           <t>S1-32649692000</t>
         </is>
       </c>
-      <c r="C419" s="4" t="inlineStr"/>
-      <c r="D419" s="4" t="inlineStr">
-        <is>
-          <t>Not searched</t>
-        </is>
-      </c>
-      <c r="E419" s="4" t="inlineStr">
-        <is>
-          <t>Not searched: per-turn web search limit reached.</t>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>York Furnace Draft Inducer Combustion Blower Motor Assembly (90%) - S1-32649692000</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Many sellers agree; fit lists vary</t>
         </is>
       </c>
     </row>
